--- a/data/leagues/EBC League 2026.xlsx
+++ b/data/leagues/EBC League 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="87">
   <si>
     <t>P90 Asiimov</t>
   </si>
@@ -49,10 +49,13 @@
     <t xml:space="preserve">First down syndrome </t>
   </si>
   <si>
-    <t>0-1-0</t>
-  </si>
-  <si>
-    <t>1-0-0</t>
+    <t>1-1-0</t>
+  </si>
+  <si>
+    <t>0-2-0</t>
+  </si>
+  <si>
+    <t>2-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -106,6 +109,9 @@
     <t>Week_2</t>
   </si>
   <si>
+    <t>Week_3</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -130,27 +136,27 @@
     <t>Jackson Jansorn</t>
   </si>
   <si>
+    <t>Mike Zacierka</t>
+  </si>
+  <si>
     <t>Kate Zacierka</t>
   </si>
   <si>
-    <t>Mike Zacierka</t>
+    <t>Alina Wise</t>
+  </si>
+  <si>
+    <t>jack meehan</t>
+  </si>
+  <si>
+    <t>Louis Rodriguez</t>
   </si>
   <si>
     <t>Derek Alcavage</t>
   </si>
   <si>
-    <t>Alina Wise</t>
-  </si>
-  <si>
     <t>Gianpierre Lopez</t>
   </si>
   <si>
-    <t>Louis Rodriguez</t>
-  </si>
-  <si>
-    <t>jack meehan</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -175,52 +181,52 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>1-0</t>
-  </si>
-  <si>
-    <t>0-1</t>
-  </si>
-  <si>
-    <t>10.6-3.3-0.1</t>
-  </si>
-  <si>
-    <t>10.1-3.8-0.1</t>
-  </si>
-  <si>
-    <t>9.5-4.4-0.1</t>
-  </si>
-  <si>
-    <t>6.5-7.4-0.1</t>
-  </si>
-  <si>
-    <t>6.4-7.5-0.1</t>
-  </si>
-  <si>
-    <t>4.9-9.0-0.1</t>
-  </si>
-  <si>
-    <t>5.0-8.9-0.1</t>
-  </si>
-  <si>
-    <t>2.6-11.3-0.1</t>
-  </si>
-  <si>
-    <t>11-3</t>
+    <t>1-1</t>
+  </si>
+  <si>
+    <t>2-0</t>
+  </si>
+  <si>
+    <t>0-2</t>
+  </si>
+  <si>
+    <t>8.9-5.0-0.1</t>
+  </si>
+  <si>
+    <t>12.1-1.8-0.1</t>
+  </si>
+  <si>
+    <t>10.3-3.6-0.1</t>
+  </si>
+  <si>
+    <t>9.3-4.6-0.1</t>
+  </si>
+  <si>
+    <t>5.3-8.5-0.1</t>
+  </si>
+  <si>
+    <t>4.6-9.3-0.1</t>
+  </si>
+  <si>
+    <t>2.8-11.2-0.1</t>
+  </si>
+  <si>
+    <t>2.3-11.6-0.1</t>
+  </si>
+  <si>
+    <t>9-5</t>
+  </si>
+  <si>
+    <t>12-2</t>
   </si>
   <si>
     <t>10-4</t>
   </si>
   <si>
-    <t>6-8</t>
-  </si>
-  <si>
-    <t>7-7</t>
-  </si>
-  <si>
     <t>5-9</t>
   </si>
   <si>
-    <t>4-10</t>
+    <t>3-11</t>
   </si>
   <si>
     <t>2-12</t>
@@ -235,7 +241,28 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑8</t>
+  </si>
+  <si>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>↑5</t>
+  </si>
+  <si>
+    <t>↓8</t>
+  </si>
+  <si>
+    <t>↓10</t>
+  </si>
+  <si>
+    <t>↓2</t>
+  </si>
+  <si>
     <t>Week 1</t>
+  </si>
+  <si>
+    <t>Week 2</t>
   </si>
   <si>
     <t>Week</t>
@@ -660,16 +687,16 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" t="s">
         <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -677,28 +704,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -712,22 +739,22 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -735,28 +762,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -767,25 +794,25 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -793,28 +820,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G7" t="s">
         <v>8</v>
       </c>
       <c r="H7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -822,28 +849,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8" t="s">
         <v>8</v>
       </c>
       <c r="H8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -851,28 +878,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G9" t="s">
         <v>8</v>
       </c>
       <c r="H9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -887,25 +914,25 @@
   <sheetData>
     <row r="1" spans="2:8">
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -920,13 +947,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -937,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.125</v>
+        <v>0.625</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -948,13 +975,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -962,13 +989,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -976,13 +1003,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>0.375</v>
+        <v>1.125</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -993,10 +1020,10 @@
         <v>3</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>1.125</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1004,13 +1031,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>0.625</v>
+        <v>1.125</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1018,10 +1045,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>0.875</v>
+        <v>1.25</v>
       </c>
       <c r="D8" t="s">
         <v>8</v>
@@ -1032,10 +1059,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>0.875</v>
+        <v>1.25</v>
       </c>
       <c r="D9" t="s">
         <v>9</v>
@@ -1053,16 +1080,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1070,16 +1097,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1087,16 +1114,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>0.875</v>
+        <v>1.75</v>
       </c>
       <c r="D3">
-        <v>-0.125</v>
+        <v>-0.25</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1104,16 +1131,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>0.75</v>
+        <v>1.375</v>
       </c>
       <c r="D4">
-        <v>-0.25</v>
+        <v>0.375</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1121,13 +1148,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="D5">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1138,13 +1165,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="D6">
-        <v>0.375</v>
+        <v>-0.25</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1158,13 +1185,13 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="D7">
-        <v>-0.75</v>
+        <v>-0.375</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1181,7 +1208,7 @@
         <v>0.25</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1192,13 +1219,13 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1213,57 +1240,57 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B2">
+        <v>1.8</v>
+      </c>
+      <c r="C2">
+        <v>12.1</v>
+      </c>
+      <c r="D2">
+        <v>31.9</v>
+      </c>
+      <c r="E2">
         <v>49.9</v>
       </c>
-      <c r="C2">
-        <v>30.4</v>
-      </c>
-      <c r="D2">
-        <v>15.6</v>
-      </c>
-      <c r="E2">
-        <v>3.1</v>
-      </c>
       <c r="F2">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1277,25 +1304,25 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>32.3</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="C3">
-        <v>35.7</v>
+        <v>16.3</v>
       </c>
       <c r="D3">
-        <v>25.2</v>
+        <v>3.5</v>
       </c>
       <c r="E3">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="F3">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1309,162 +1336,162 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>16.4</v>
+        <v>14.9</v>
       </c>
       <c r="C4">
-        <v>29.9</v>
+        <v>45.3</v>
       </c>
       <c r="D4">
-        <v>39.2</v>
+        <v>25.7</v>
       </c>
       <c r="E4">
-        <v>10.5</v>
+        <v>13.2</v>
       </c>
       <c r="F4">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="G4">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="H4">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>25.6</v>
       </c>
       <c r="D5">
-        <v>9.1</v>
+        <v>37.4</v>
       </c>
       <c r="E5">
-        <v>32.5</v>
+        <v>30.2</v>
       </c>
       <c r="F5">
-        <v>29.8</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>15.9</v>
+        <v>0.1</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>89.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="D6">
-        <v>7.6</v>
+        <v>1.3</v>
       </c>
       <c r="E6">
-        <v>31.9</v>
+        <v>4.3</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>51.9</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>29.7</v>
       </c>
       <c r="H6">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="I6">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J6">
-        <v>88.7</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B7">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
         <v>0.2</v>
       </c>
-      <c r="D7">
-        <v>1.4</v>
-      </c>
       <c r="E7">
-        <v>8.6</v>
+        <v>1.6</v>
       </c>
       <c r="F7">
-        <v>18.6</v>
+        <v>33.8</v>
       </c>
       <c r="G7">
-        <v>29.2</v>
+        <v>48.8</v>
       </c>
       <c r="H7">
-        <v>31.8</v>
+        <v>12.9</v>
       </c>
       <c r="I7">
-        <v>10.1</v>
+        <v>2.7</v>
       </c>
       <c r="J7">
-        <v>58.1</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B8">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
         <v>0.2</v>
       </c>
-      <c r="D8">
-        <v>1.9</v>
-      </c>
-      <c r="E8">
-        <v>8.5</v>
-      </c>
       <c r="F8">
-        <v>17.5</v>
+        <v>4.5</v>
       </c>
       <c r="G8">
-        <v>28.9</v>
+        <v>13.8</v>
       </c>
       <c r="H8">
-        <v>34.4</v>
+        <v>38.2</v>
       </c>
       <c r="I8">
-        <v>8.5</v>
+        <v>43.3</v>
       </c>
       <c r="J8">
-        <v>57.1</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1481,22 +1508,22 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="H9">
-        <v>16.3</v>
+        <v>39.4</v>
       </c>
       <c r="I9">
-        <v>77.09999999999999</v>
+        <v>51.4</v>
       </c>
       <c r="J9">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1506,29 +1533,35 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>27</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2">
-        <v>99.40000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="C2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1538,71 +1571,92 @@
       <c r="C3">
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B5">
-        <v>88</v>
+        <v>87.2</v>
       </c>
       <c r="C5">
-        <v>89.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>100</v>
+      </c>
+      <c r="D5">
+        <v>99.90000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>88.90000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="C6">
-        <v>86.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>90.2</v>
+      </c>
+      <c r="D6">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B7">
-        <v>65.10000000000001</v>
+        <v>63.7</v>
       </c>
       <c r="C7">
-        <v>62.1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>81.69999999999999</v>
+      </c>
+      <c r="D7">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B8">
-        <v>51</v>
+        <v>54.8</v>
       </c>
       <c r="C8">
-        <v>56.49999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>20.1</v>
+      </c>
+      <c r="D8">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B9">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="C9">
-        <v>5.4</v>
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>11.7</v>
       </c>
     </row>
   </sheetData>
@@ -1617,28 +1671,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1649,25 +1703,25 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D2">
-        <v>97.40000000000001</v>
+        <v>103.09</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>135.4</v>
+        <v>128.69</v>
       </c>
       <c r="G2">
-        <v>0.538</v>
+        <v>0.542</v>
       </c>
       <c r="H2">
         <v>2.2</v>
       </c>
       <c r="I2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1675,28 +1729,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D3">
-        <v>113.22</v>
+        <v>99.48</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3">
-        <v>134.18</v>
+        <v>129.46</v>
       </c>
       <c r="G3">
-        <v>0.462</v>
+        <v>0.583</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1704,28 +1758,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D4">
-        <v>116.2</v>
+        <v>112.82</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4">
-        <v>129.57</v>
+        <v>128.35</v>
       </c>
       <c r="G4">
-        <v>0.538</v>
+        <v>0.542</v>
       </c>
       <c r="H4">
-        <v>-0.2</v>
+        <v>1.7</v>
       </c>
       <c r="I4">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1733,28 +1787,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D5">
-        <v>151.4</v>
+        <v>113.39</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>126.86</v>
+        <v>127.16</v>
       </c>
       <c r="G5">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="H5">
-        <v>-0.5</v>
+        <v>1.2</v>
       </c>
       <c r="I5">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1762,28 +1816,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6">
-        <v>128.52</v>
+        <v>142.9</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>128.16</v>
+        <v>123.34</v>
       </c>
       <c r="G6">
-        <v>0.538</v>
+        <v>0.458</v>
       </c>
       <c r="H6">
-        <v>-0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1791,28 +1845,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D7">
-        <v>145.16</v>
+        <v>137.18</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>126.88</v>
+        <v>123</v>
       </c>
       <c r="G7">
-        <v>0.462</v>
+        <v>0.458</v>
       </c>
       <c r="H7">
-        <v>-0.8</v>
+        <v>-1.2</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1820,28 +1874,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D8">
-        <v>127.26</v>
+        <v>140.26</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8">
-        <v>127.6</v>
+        <v>122.68</v>
       </c>
       <c r="G8">
-        <v>0.538</v>
+        <v>0.5</v>
       </c>
       <c r="H8">
-        <v>-0.9</v>
+        <v>-1.2</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1849,28 +1903,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D9">
-        <v>154.96</v>
+        <v>153.94</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>125.47</v>
+        <v>120.38</v>
       </c>
       <c r="G9">
-        <v>0.462</v>
+        <v>0.417</v>
       </c>
       <c r="H9">
-        <v>-1.2</v>
+        <v>-1.8</v>
       </c>
       <c r="I9">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1885,48 +1939,48 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D2">
-        <v>154.96</v>
+        <v>137.18</v>
       </c>
       <c r="E2">
-        <v>154.96</v>
+        <v>274.36</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -1935,27 +1989,27 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>151.4</v>
+        <v>153.94</v>
       </c>
       <c r="E3">
-        <v>151.4</v>
+        <v>307.88</v>
       </c>
       <c r="F3">
         <v>100</v>
@@ -1964,155 +2018,155 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>145.16</v>
+        <v>142.9</v>
       </c>
       <c r="E4">
-        <v>145.16</v>
+        <v>285.8</v>
       </c>
       <c r="F4">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D5">
-        <v>128.52</v>
+        <v>140.26</v>
       </c>
       <c r="E5">
-        <v>128.52</v>
+        <v>280.52</v>
       </c>
       <c r="F5">
-        <v>89.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>127.26</v>
+        <v>113.39</v>
       </c>
       <c r="E6">
-        <v>127.26</v>
+        <v>226.78</v>
       </c>
       <c r="F6">
-        <v>88.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G6">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="H6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>116.2</v>
+        <v>112.82</v>
       </c>
       <c r="E7">
-        <v>116.2</v>
+        <v>225.64</v>
       </c>
       <c r="F7">
-        <v>58.09999999999999</v>
+        <v>84.39999999999999</v>
       </c>
       <c r="G7">
-        <v>10.1</v>
+        <v>2.7</v>
       </c>
       <c r="H7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>113.22</v>
+        <v>99.48</v>
       </c>
       <c r="E8">
-        <v>113.22</v>
+        <v>198.96</v>
       </c>
       <c r="F8">
-        <v>57.09999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="G8">
-        <v>8.5</v>
+        <v>43.3</v>
       </c>
       <c r="H8" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2120,28 +2174,28 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>97.40000000000001</v>
+        <v>103.09</v>
       </c>
       <c r="E9">
-        <v>97.40000000000001</v>
+        <v>206.18</v>
       </c>
       <c r="F9">
-        <v>6.600000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G9">
-        <v>77.10000000000001</v>
+        <v>51.4</v>
       </c>
       <c r="H9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -2156,19 +2210,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2176,19 +2230,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2196,19 +2250,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2219,16 +2273,16 @@
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
-      <c r="F4">
-        <v>0</v>
+      <c r="F4" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2239,16 +2293,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2259,16 +2313,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
-      <c r="F6">
-        <v>0</v>
+      <c r="F6" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2276,19 +2330,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
-      <c r="F7">
-        <v>0</v>
+      <c r="F7" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2296,19 +2350,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D8">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
-      <c r="F8">
-        <v>0</v>
+      <c r="F8" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2319,16 +2373,16 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D9">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -2338,40 +2392,49 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>79</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
+      <c r="B3">
         <v>6</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
       <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -2379,10 +2442,13 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -2390,10 +2456,13 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -2401,32 +2470,41 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>-6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>-8</v>
+      </c>
+      <c r="C7">
+        <v>-6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="B8">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>-10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -2434,7 +2512,10 @@
         <v>-10</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>-12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/EBC League 2026.xlsx
+++ b/data/leagues/EBC League 2026.xlsx
@@ -190,25 +190,25 @@
     <t>0-2</t>
   </si>
   <si>
-    <t>8.9-5.0-0.1</t>
-  </si>
-  <si>
-    <t>12.1-1.8-0.1</t>
-  </si>
-  <si>
-    <t>10.3-3.6-0.1</t>
-  </si>
-  <si>
-    <t>9.3-4.6-0.1</t>
-  </si>
-  <si>
-    <t>5.3-8.5-0.1</t>
+    <t>8.8-5.1-0.1</t>
+  </si>
+  <si>
+    <t>12.2-1.8-0.1</t>
+  </si>
+  <si>
+    <t>10.2-3.7-0.1</t>
+  </si>
+  <si>
+    <t>9.4-4.5-0.1</t>
+  </si>
+  <si>
+    <t>5.4-8.5-0.1</t>
   </si>
   <si>
     <t>4.6-9.3-0.1</t>
   </si>
   <si>
-    <t>2.8-11.2-0.1</t>
+    <t>2.8-11.1-0.1</t>
   </si>
   <si>
     <t>2.3-11.6-0.1</t>
@@ -1275,22 +1275,22 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="C2">
-        <v>12.1</v>
+        <v>13.8</v>
       </c>
       <c r="D2">
-        <v>31.9</v>
+        <v>30.2</v>
       </c>
       <c r="E2">
-        <v>49.9</v>
+        <v>48.7</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1307,16 +1307,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>79.59999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="C3">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="D3">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="E3">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1339,19 +1339,19 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>14.9</v>
+        <v>13.6</v>
       </c>
       <c r="C4">
-        <v>45.3</v>
+        <v>41.4</v>
       </c>
       <c r="D4">
-        <v>25.7</v>
+        <v>29.7</v>
       </c>
       <c r="E4">
-        <v>13.2</v>
+        <v>14.7</v>
       </c>
       <c r="F4">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G4">
         <v>0.1</v>
@@ -1371,22 +1371,22 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="C5">
-        <v>25.6</v>
+        <v>27.9</v>
       </c>
       <c r="D5">
-        <v>37.4</v>
+        <v>36</v>
       </c>
       <c r="E5">
-        <v>30.2</v>
+        <v>28.7</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G5">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1406,28 +1406,28 @@
         <v>0</v>
       </c>
       <c r="C6">
+        <v>0.4</v>
+      </c>
+      <c r="D6">
         <v>0.7</v>
       </c>
-      <c r="D6">
-        <v>1.3</v>
-      </c>
       <c r="E6">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="F6">
-        <v>51.9</v>
+        <v>52.4</v>
       </c>
       <c r="G6">
-        <v>29.7</v>
+        <v>29.3</v>
       </c>
       <c r="H6">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J6">
-        <v>87.90000000000001</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1441,25 +1441,25 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E7">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="F7">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="G7">
-        <v>48.8</v>
+        <v>46.8</v>
       </c>
       <c r="H7">
-        <v>12.9</v>
+        <v>16</v>
       </c>
       <c r="I7">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J7">
-        <v>84.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1476,22 +1476,22 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F8">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="G8">
-        <v>13.8</v>
+        <v>14.5</v>
       </c>
       <c r="H8">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="I8">
-        <v>43.3</v>
+        <v>42.8</v>
       </c>
       <c r="J8">
-        <v>18.5</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1511,19 +1511,19 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="G9">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="H9">
-        <v>39.4</v>
+        <v>36.9</v>
       </c>
       <c r="I9">
-        <v>51.4</v>
+        <v>52.9</v>
       </c>
       <c r="J9">
-        <v>9.199999999999999</v>
+        <v>10.2</v>
       </c>
     </row>
   </sheetData>
@@ -1549,10 +1549,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2">
-        <v>99.7</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -1591,16 +1591,16 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>87.2</v>
+        <v>100</v>
       </c>
       <c r="C5">
         <v>100</v>
       </c>
       <c r="D5">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1611,10 +1611,10 @@
         <v>89.3</v>
       </c>
       <c r="C6">
-        <v>90.2</v>
+        <v>91</v>
       </c>
       <c r="D6">
-        <v>86</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1622,13 +1622,13 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>63.7</v>
+        <v>65.5</v>
       </c>
       <c r="C7">
-        <v>81.69999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="D7">
-        <v>83</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1636,13 +1636,13 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <v>54.8</v>
+        <v>52.3</v>
       </c>
       <c r="C8">
-        <v>20.1</v>
+        <v>21.8</v>
       </c>
       <c r="D8">
-        <v>19.4</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1650,13 +1650,13 @@
         <v>6</v>
       </c>
       <c r="B9">
-        <v>5.4</v>
+        <v>7.3</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D9">
-        <v>11.7</v>
+        <v>9.700000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2079,7 +2079,7 @@
         <v>58</v>
       </c>
       <c r="I5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2099,10 +2099,10 @@
         <v>226.78</v>
       </c>
       <c r="F6">
-        <v>87.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="G6">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="H6" t="s">
         <v>59</v>
@@ -2128,10 +2128,10 @@
         <v>225.64</v>
       </c>
       <c r="F7">
-        <v>84.39999999999999</v>
+        <v>81.89999999999999</v>
       </c>
       <c r="G7">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="H7" t="s">
         <v>60</v>
@@ -2157,10 +2157,10 @@
         <v>198.96</v>
       </c>
       <c r="F8">
-        <v>18.5</v>
+        <v>18.9</v>
       </c>
       <c r="G8">
-        <v>43.3</v>
+        <v>42.8</v>
       </c>
       <c r="H8" t="s">
         <v>61</v>
@@ -2186,10 +2186,10 @@
         <v>206.18</v>
       </c>
       <c r="F9">
-        <v>9.199999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="G9">
-        <v>51.4</v>
+        <v>52.90000000000001</v>
       </c>
       <c r="H9" t="s">
         <v>62</v>

--- a/data/leagues/EBC League 2026.xlsx
+++ b/data/leagues/EBC League 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="89">
   <si>
     <t>P90 Asiimov</t>
   </si>
@@ -49,13 +49,16 @@
     <t xml:space="preserve">First down syndrome </t>
   </si>
   <si>
-    <t>1-1-0</t>
-  </si>
-  <si>
-    <t>0-2-0</t>
-  </si>
-  <si>
-    <t>2-0-0</t>
+    <t>1-2-0</t>
+  </si>
+  <si>
+    <t>2-1-0</t>
+  </si>
+  <si>
+    <t>3-0-0</t>
+  </si>
+  <si>
+    <t>0-3-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -112,6 +115,9 @@
     <t>Week_3</t>
   </si>
   <si>
+    <t>Week_4</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -136,21 +142,21 @@
     <t>Jackson Jansorn</t>
   </si>
   <si>
+    <t>Kate Zacierka</t>
+  </si>
+  <si>
+    <t>Louis Rodriguez</t>
+  </si>
+  <si>
     <t>Mike Zacierka</t>
   </si>
   <si>
-    <t>Kate Zacierka</t>
-  </si>
-  <si>
     <t>Alina Wise</t>
   </si>
   <si>
     <t>jack meehan</t>
   </si>
   <si>
-    <t>Louis Rodriguez</t>
-  </si>
-  <si>
     <t>Derek Alcavage</t>
   </si>
   <si>
@@ -181,46 +187,43 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>8.8-5.1-0.1</t>
-  </si>
-  <si>
-    <t>12.2-1.8-0.1</t>
-  </si>
-  <si>
-    <t>10.2-3.7-0.1</t>
-  </si>
-  <si>
-    <t>9.4-4.5-0.1</t>
-  </si>
-  <si>
-    <t>5.4-8.5-0.1</t>
-  </si>
-  <si>
-    <t>4.6-9.3-0.1</t>
-  </si>
-  <si>
-    <t>2.8-11.1-0.1</t>
-  </si>
-  <si>
-    <t>2.3-11.6-0.1</t>
-  </si>
-  <si>
-    <t>9-5</t>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>0-3</t>
+  </si>
+  <si>
+    <t>12.0-1.9-0.1</t>
+  </si>
+  <si>
+    <t>11.4-2.5-0.1</t>
+  </si>
+  <si>
+    <t>6.8-7.1-0.2</t>
+  </si>
+  <si>
+    <t>6.9-7.0-0.2</t>
+  </si>
+  <si>
+    <t>5.1-8.8-0.2</t>
+  </si>
+  <si>
+    <t>3.5-10.3-0.1</t>
+  </si>
+  <si>
+    <t>3.0-10.9-0.1</t>
   </si>
   <si>
     <t>12-2</t>
   </si>
   <si>
-    <t>10-4</t>
+    <t>7-7</t>
   </si>
   <si>
     <t>5-9</t>
@@ -229,9 +232,6 @@
     <t>3-11</t>
   </si>
   <si>
-    <t>2-12</t>
-  </si>
-  <si>
     <t>Owners</t>
   </si>
   <si>
@@ -241,28 +241,34 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑8</t>
-  </si>
-  <si>
-    <t>↑2</t>
-  </si>
-  <si>
-    <t>↑5</t>
+    <t>↑4</t>
+  </si>
+  <si>
+    <t>↑6</t>
+  </si>
+  <si>
+    <t>↓4</t>
   </si>
   <si>
     <t>↓8</t>
   </si>
   <si>
-    <t>↓10</t>
-  </si>
-  <si>
-    <t>↓2</t>
+    <t>↑3</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>↑1</t>
   </si>
   <si>
     <t>Week 1</t>
   </si>
   <si>
     <t>Week 2</t>
+  </si>
+  <si>
+    <t>Week 3</t>
   </si>
   <si>
     <t>Week</t>
@@ -690,13 +696,13 @@
         <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -704,25 +710,25 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
         <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" t="s">
-        <v>8</v>
       </c>
       <c r="I3" t="s">
         <v>8</v>
@@ -733,10 +739,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -745,7 +751,7 @@
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" t="s">
         <v>10</v>
@@ -754,7 +760,7 @@
         <v>10</v>
       </c>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -774,7 +780,7 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" t="s">
         <v>10</v>
@@ -783,7 +789,7 @@
         <v>10</v>
       </c>
       <c r="I5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -794,19 +800,19 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
         <v>8</v>
       </c>
       <c r="G6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -820,25 +826,25 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
         <v>9</v>
       </c>
-      <c r="C7" t="s">
-        <v>8</v>
-      </c>
       <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s">
         <v>9</v>
       </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
       <c r="F7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7" t="s">
         <v>8</v>
@@ -849,28 +855,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" t="s">
         <v>9</v>
       </c>
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" t="s">
-        <v>8</v>
-      </c>
       <c r="H8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -878,25 +884,25 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="H9" t="s">
         <v>9</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" t="s">
-        <v>8</v>
-      </c>
-      <c r="H9" t="s">
-        <v>8</v>
       </c>
       <c r="I9" t="s">
         <v>8</v>
@@ -909,30 +915,82 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:8">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>-16</v>
+      </c>
+      <c r="G2">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>-6</v>
+      </c>
+      <c r="G3">
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -947,13 +1005,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -961,10 +1019,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -978,7 +1036,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>0.75</v>
+        <v>1.125</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -989,10 +1047,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
@@ -1003,13 +1061,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>1.125</v>
+        <v>1.375</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1017,13 +1075,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>1.125</v>
+        <v>1.5</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1031,13 +1089,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>1.125</v>
+        <v>1.625</v>
       </c>
       <c r="D7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1045,10 +1103,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="D8" t="s">
         <v>8</v>
@@ -1059,10 +1117,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>1.25</v>
+        <v>2.125</v>
       </c>
       <c r="D9" t="s">
         <v>9</v>
@@ -1080,16 +1138,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1097,10 +1155,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="D2">
         <v>-0.25</v>
@@ -1114,13 +1172,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="D3">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -1131,16 +1189,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>1.375</v>
+        <v>1.625</v>
       </c>
       <c r="D4">
-        <v>0.375</v>
+        <v>-0.375</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1151,10 +1209,10 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>1.25</v>
+        <v>1.375</v>
       </c>
       <c r="D5">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1165,13 +1223,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>0.75</v>
+        <v>1.375</v>
       </c>
       <c r="D6">
-        <v>-0.25</v>
+        <v>0.375</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1185,10 +1243,10 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>-0.375</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1202,13 +1260,13 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="D8">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1219,13 +1277,13 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="D9">
-        <v>0.25</v>
+        <v>-0.375</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1240,57 +1298,57 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2">
-        <v>1.9</v>
+        <v>64.2</v>
       </c>
       <c r="C2">
-        <v>13.8</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>30.2</v>
+        <v>1.7</v>
       </c>
       <c r="E2">
-        <v>48.7</v>
+        <v>0.1</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1304,19 +1362,19 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3">
-        <v>79.90000000000001</v>
+        <v>35.4</v>
       </c>
       <c r="C3">
-        <v>16.5</v>
+        <v>61</v>
       </c>
       <c r="D3">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="E3">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1336,34 +1394,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B4">
-        <v>13.6</v>
+        <v>0.3</v>
       </c>
       <c r="C4">
-        <v>41.4</v>
+        <v>0.9</v>
       </c>
       <c r="D4">
-        <v>29.7</v>
+        <v>32.1</v>
       </c>
       <c r="E4">
-        <v>14.7</v>
+        <v>29.3</v>
       </c>
       <c r="F4">
-        <v>0.5</v>
+        <v>24.8</v>
       </c>
       <c r="G4">
-        <v>0.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1371,31 +1429,31 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>4.6</v>
+        <v>0.1</v>
       </c>
       <c r="C5">
-        <v>27.9</v>
+        <v>2.3</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>30.2</v>
       </c>
       <c r="E5">
-        <v>28.7</v>
+        <v>30.1</v>
       </c>
       <c r="F5">
-        <v>2.5</v>
+        <v>23.1</v>
       </c>
       <c r="G5">
-        <v>0.3</v>
+        <v>10.8</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1406,28 +1464,28 @@
         <v>0</v>
       </c>
       <c r="C6">
+        <v>1.8</v>
+      </c>
+      <c r="D6">
+        <v>27.5</v>
+      </c>
+      <c r="E6">
+        <v>27.3</v>
+      </c>
+      <c r="F6">
+        <v>26.9</v>
+      </c>
+      <c r="G6">
+        <v>12.6</v>
+      </c>
+      <c r="H6">
+        <v>3.5</v>
+      </c>
+      <c r="I6">
         <v>0.4</v>
       </c>
-      <c r="D6">
-        <v>0.7</v>
-      </c>
-      <c r="E6">
-        <v>6.2</v>
-      </c>
-      <c r="F6">
-        <v>52.4</v>
-      </c>
-      <c r="G6">
-        <v>29.3</v>
-      </c>
-      <c r="H6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="I6">
-        <v>2.2</v>
-      </c>
       <c r="J6">
-        <v>89</v>
+        <v>96.09999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1441,30 +1499,30 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0.3</v>
+        <v>4.2</v>
       </c>
       <c r="E7">
-        <v>1.1</v>
+        <v>11.2</v>
       </c>
       <c r="F7">
-        <v>33.7</v>
+        <v>19.3</v>
       </c>
       <c r="G7">
-        <v>46.8</v>
+        <v>41.2</v>
       </c>
       <c r="H7">
-        <v>16</v>
+        <v>17.7</v>
       </c>
       <c r="I7">
-        <v>2.1</v>
+        <v>6.4</v>
       </c>
       <c r="J7">
-        <v>81.90000000000001</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1473,30 +1531,30 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E8">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="F8">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="G8">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="H8">
-        <v>38.3</v>
+        <v>42</v>
       </c>
       <c r="I8">
-        <v>42.8</v>
+        <v>38.2</v>
       </c>
       <c r="J8">
-        <v>18.9</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1505,25 +1563,25 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="F9">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="G9">
-        <v>8.6</v>
+        <v>11.8</v>
       </c>
       <c r="H9">
-        <v>36.9</v>
+        <v>32.1</v>
       </c>
       <c r="I9">
         <v>52.9</v>
       </c>
       <c r="J9">
-        <v>10.2</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1533,26 +1591,29 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>29</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2">
-        <v>85.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -1560,13 +1621,16 @@
       <c r="D2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -1574,89 +1638,110 @@
       <c r="D3">
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B4">
-        <v>100</v>
+        <v>93.7</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4">
+        <v>98</v>
+      </c>
+      <c r="E4">
+        <v>95.89999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>93.2</v>
+      </c>
+      <c r="C5">
+        <v>91.7</v>
+      </c>
+      <c r="D5">
+        <v>96.3</v>
+      </c>
+      <c r="E5">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
+      <c r="C6">
         <v>100</v>
       </c>
-      <c r="C5">
-        <v>100</v>
-      </c>
-      <c r="D5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>89.3</v>
-      </c>
-      <c r="C6">
-        <v>91</v>
-      </c>
       <c r="D6">
-        <v>88.8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>96.5</v>
+      </c>
+      <c r="E6">
+        <v>95.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B7">
-        <v>65.5</v>
+        <v>62</v>
       </c>
       <c r="C7">
-        <v>81.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D7">
-        <v>83.3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>75.5</v>
+      </c>
+      <c r="E7">
+        <v>77.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>1.5</v>
+      </c>
+      <c r="C8">
+        <v>11.3</v>
+      </c>
+      <c r="D8">
+        <v>20.2</v>
+      </c>
+      <c r="E8">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B8">
-        <v>52.3</v>
-      </c>
-      <c r="C8">
-        <v>21.8</v>
-      </c>
-      <c r="D8">
-        <v>18.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="B9">
-        <v>7.3</v>
+        <v>49.6</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>10.6</v>
       </c>
       <c r="D9">
-        <v>9.700000000000001</v>
+        <v>13.5</v>
+      </c>
+      <c r="E9">
+        <v>14.9</v>
       </c>
     </row>
   </sheetData>
@@ -1671,28 +1756,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1703,25 +1788,25 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2">
-        <v>103.09</v>
+        <v>107.74</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>128.69</v>
+        <v>126.61</v>
       </c>
       <c r="G2">
-        <v>0.542</v>
+        <v>0.515</v>
       </c>
       <c r="H2">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1729,28 +1814,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3">
-        <v>99.48</v>
+        <v>117.23</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>129.46</v>
+        <v>125.75</v>
       </c>
       <c r="G3">
-        <v>0.583</v>
+        <v>0.515</v>
       </c>
       <c r="H3">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1758,28 +1843,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4">
-        <v>112.82</v>
+        <v>126.7</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4">
-        <v>128.35</v>
+        <v>124.88</v>
       </c>
       <c r="G4">
-        <v>0.542</v>
+        <v>0.515</v>
       </c>
       <c r="H4">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="I4">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1787,28 +1872,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D5">
-        <v>113.39</v>
+        <v>108.78</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>127.16</v>
+        <v>125.81</v>
       </c>
       <c r="G5">
-        <v>0.5</v>
+        <v>0.545</v>
       </c>
       <c r="H5">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="I5">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1816,28 +1901,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D6">
-        <v>142.9</v>
+        <v>120.93</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>123.34</v>
+        <v>124.71</v>
       </c>
       <c r="G6">
-        <v>0.458</v>
+        <v>0.485</v>
       </c>
       <c r="H6">
-        <v>-0.7</v>
+        <v>0.1</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1845,28 +1930,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D7">
-        <v>137.18</v>
+        <v>143.31</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>123</v>
+        <v>123.37</v>
       </c>
       <c r="G7">
-        <v>0.458</v>
+        <v>0.455</v>
       </c>
       <c r="H7">
-        <v>-1.2</v>
+        <v>-0.8</v>
       </c>
       <c r="I7">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1877,25 +1962,25 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D8">
-        <v>140.26</v>
+        <v>126.31</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8">
-        <v>122.68</v>
+        <v>124.22</v>
       </c>
       <c r="G8">
-        <v>0.5</v>
+        <v>0.515</v>
       </c>
       <c r="H8">
-        <v>-1.2</v>
+        <v>-0.8</v>
       </c>
       <c r="I8">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1906,25 +1991,25 @@
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D9">
-        <v>153.94</v>
+        <v>146.71</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9">
-        <v>120.38</v>
+        <v>122.36</v>
       </c>
       <c r="G9">
-        <v>0.417</v>
+        <v>0.455</v>
       </c>
       <c r="H9">
-        <v>-1.8</v>
+        <v>-1.9</v>
       </c>
       <c r="I9">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1939,48 +2024,48 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C2">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>137.18</v>
+        <v>146.7133333333333</v>
       </c>
       <c r="E2">
-        <v>274.36</v>
+        <v>440.14</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -1989,27 +2074,27 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>153.94</v>
+        <v>143.3133333333333</v>
       </c>
       <c r="E3">
-        <v>307.88</v>
+        <v>429.94</v>
       </c>
       <c r="F3">
         <v>100</v>
@@ -2018,39 +2103,39 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D4">
-        <v>142.9</v>
+        <v>126.7</v>
       </c>
       <c r="E4">
-        <v>285.8</v>
+        <v>380.1</v>
       </c>
       <c r="F4">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="H4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2058,28 +2143,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C5">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D5">
-        <v>140.26</v>
+        <v>126.3066666666667</v>
       </c>
       <c r="E5">
-        <v>280.52</v>
+        <v>378.92</v>
       </c>
       <c r="F5">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="H5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2087,25 +2172,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D6">
-        <v>113.39</v>
+        <v>120.9266666666667</v>
       </c>
       <c r="E6">
-        <v>226.78</v>
+        <v>362.78</v>
       </c>
       <c r="F6">
-        <v>89</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="G6">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="H6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I6" t="s">
         <v>66</v>
@@ -2116,83 +2201,83 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D7">
-        <v>112.82</v>
+        <v>117.2266666666667</v>
       </c>
       <c r="E7">
-        <v>225.64</v>
+        <v>351.68</v>
       </c>
       <c r="F7">
-        <v>81.89999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G7">
-        <v>2.1</v>
+        <v>6.4</v>
       </c>
       <c r="H7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D8">
-        <v>99.48</v>
+        <v>107.74</v>
       </c>
       <c r="E8">
-        <v>198.96</v>
+        <v>323.22</v>
       </c>
       <c r="F8">
-        <v>18.9</v>
+        <v>19.8</v>
       </c>
       <c r="G8">
-        <v>42.8</v>
+        <v>38.2</v>
       </c>
       <c r="H8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>103.09</v>
+        <v>108.78</v>
       </c>
       <c r="E9">
-        <v>206.18</v>
+        <v>326.34</v>
       </c>
       <c r="F9">
-        <v>10.2</v>
+        <v>15</v>
       </c>
       <c r="G9">
         <v>52.90000000000001</v>
       </c>
       <c r="H9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I9" t="s">
         <v>68</v>
@@ -2210,7 +2295,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>69</v>
@@ -2219,7 +2304,7 @@
         <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>71</v>
@@ -2233,10 +2318,10 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -2253,10 +2338,10 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -2270,13 +2355,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -2290,19 +2375,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2310,19 +2395,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
         <v>39</v>
       </c>
       <c r="D6">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2330,19 +2415,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D7">
         <v>-6</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2353,16 +2438,16 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D8">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2373,16 +2458,16 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D9">
-        <v>-12</v>
+        <v>-16</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2392,21 +2477,24 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -2416,11 +2504,14 @@
       <c r="C2">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -2430,13 +2521,16 @@
       <c r="C3">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -2444,13 +2538,16 @@
       <c r="C4">
         <v>8</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -2458,39 +2555,48 @@
       <c r="C5">
         <v>8</v>
       </c>
-      <c r="D5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="C6">
         <v>-6</v>
       </c>
-      <c r="D6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="D6">
+        <v>-3</v>
+      </c>
+      <c r="E6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7">
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="C7">
         <v>-6</v>
       </c>
-      <c r="D7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="D7">
+        <v>-6</v>
+      </c>
+      <c r="E7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
@@ -2500,11 +2606,14 @@
       <c r="C8">
         <v>-10</v>
       </c>
-      <c r="D8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="D8">
+        <v>-9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -2514,8 +2623,11 @@
       <c r="C9">
         <v>-12</v>
       </c>
-      <c r="D9" t="s">
-        <v>77</v>
+      <c r="D9">
+        <v>-16</v>
+      </c>
+      <c r="E9" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/EBC League 2026.xlsx
+++ b/data/leagues/EBC League 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="97">
   <si>
     <t>P90 Asiimov</t>
   </si>
@@ -49,16 +49,19 @@
     <t xml:space="preserve">First down syndrome </t>
   </si>
   <si>
-    <t>1-2-0</t>
-  </si>
-  <si>
-    <t>2-1-0</t>
-  </si>
-  <si>
-    <t>3-0-0</t>
-  </si>
-  <si>
-    <t>0-3-0</t>
+    <t>1-3-0</t>
+  </si>
+  <si>
+    <t>2-2-0</t>
+  </si>
+  <si>
+    <t>3-1-0</t>
+  </si>
+  <si>
+    <t>0-4-0</t>
+  </si>
+  <si>
+    <t>4-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -118,6 +121,9 @@
     <t>Week_4</t>
   </si>
   <si>
+    <t>Week_5</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -142,27 +148,27 @@
     <t>Jackson Jansorn</t>
   </si>
   <si>
+    <t>Alina Wise</t>
+  </si>
+  <si>
     <t>Kate Zacierka</t>
   </si>
   <si>
+    <t>Gianpierre Lopez</t>
+  </si>
+  <si>
+    <t>jack meehan</t>
+  </si>
+  <si>
+    <t>Mike Zacierka</t>
+  </si>
+  <si>
     <t>Louis Rodriguez</t>
   </si>
   <si>
-    <t>Mike Zacierka</t>
-  </si>
-  <si>
-    <t>Alina Wise</t>
-  </si>
-  <si>
-    <t>jack meehan</t>
-  </si>
-  <si>
     <t>Derek Alcavage</t>
   </si>
   <si>
-    <t>Gianpierre Lopez</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -187,45 +193,57 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>3-0</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>0-3</t>
-  </si>
-  <si>
-    <t>12.0-1.9-0.1</t>
-  </si>
-  <si>
-    <t>11.4-2.5-0.1</t>
-  </si>
-  <si>
-    <t>6.8-7.1-0.2</t>
-  </si>
-  <si>
-    <t>6.9-7.0-0.2</t>
-  </si>
-  <si>
-    <t>5.1-8.8-0.2</t>
-  </si>
-  <si>
-    <t>3.5-10.3-0.1</t>
-  </si>
-  <si>
-    <t>3.0-10.9-0.1</t>
+    <t>4-0</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>0-4</t>
+  </si>
+  <si>
+    <t>11.5-2.4-0.1</t>
+  </si>
+  <si>
+    <t>8.9-5.0-0.1</t>
+  </si>
+  <si>
+    <t>8.9-5.1-0.1</t>
+  </si>
+  <si>
+    <t>6.8-7.1-0.1</t>
+  </si>
+  <si>
+    <t>6.0-7.9-0.1</t>
+  </si>
+  <si>
+    <t>5.5-8.4-0.1</t>
+  </si>
+  <si>
+    <t>4.8-9.1-0.1</t>
+  </si>
+  <si>
+    <t>3.2-10.7-0.1</t>
   </si>
   <si>
     <t>12-2</t>
   </si>
   <si>
+    <t>9-5</t>
+  </si>
+  <si>
     <t>7-7</t>
   </si>
   <si>
+    <t>6-8</t>
+  </si>
+  <si>
     <t>5-9</t>
   </si>
   <si>
@@ -244,24 +262,27 @@
     <t>↑4</t>
   </si>
   <si>
+    <t>↑10</t>
+  </si>
+  <si>
+    <t>↓7</t>
+  </si>
+  <si>
     <t>↑6</t>
   </si>
   <si>
+    <t>↓5</t>
+  </si>
+  <si>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>↓6</t>
+  </si>
+  <si>
     <t>↓4</t>
   </si>
   <si>
-    <t>↓8</t>
-  </si>
-  <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>↑1</t>
-  </si>
-  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -269,6 +290,9 @@
   </si>
   <si>
     <t>Week 3</t>
+  </si>
+  <si>
+    <t>Week 4</t>
   </si>
   <si>
     <t>Week</t>
@@ -687,22 +711,22 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -716,7 +740,7 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -728,10 +752,10 @@
         <v>8</v>
       </c>
       <c r="H3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -757,7 +781,7 @@
         <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I4" t="s">
         <v>9</v>
@@ -771,25 +795,25 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" t="s">
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" t="s">
         <v>10</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -797,28 +821,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -861,22 +885,22 @@
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
         <v>11</v>
       </c>
       <c r="G8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -890,7 +914,7 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -902,10 +926,10 @@
         <v>9</v>
       </c>
       <c r="H9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -915,30 +939,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -946,25 +970,25 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="F2">
-        <v>-16</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -975,22 +999,74 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>-16</v>
+      </c>
+      <c r="G3">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D4" t="s">
         <v>5</v>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>4</v>
       </c>
-      <c r="F3">
+      <c r="F4">
         <v>-6</v>
       </c>
-      <c r="G3">
+      <c r="G4">
         <v>10</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H4" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>-20</v>
+      </c>
+      <c r="F5">
+        <v>-12</v>
+      </c>
+      <c r="G5">
+        <v>8</v>
+      </c>
+      <c r="H5" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1005,13 +1081,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1022,10 +1098,10 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1033,13 +1109,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>1.125</v>
+        <v>1.5</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1047,13 +1123,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1061,13 +1137,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>1.375</v>
+        <v>1.875</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1075,13 +1151,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1092,10 +1168,10 @@
         <v>3</v>
       </c>
       <c r="C7">
-        <v>1.625</v>
+        <v>2.125</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1103,13 +1179,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>2.625</v>
       </c>
       <c r="D8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1117,10 +1193,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>2.125</v>
+        <v>2.875</v>
       </c>
       <c r="D9" t="s">
         <v>9</v>
@@ -1138,16 +1214,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1158,13 +1234,13 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>2.75</v>
+        <v>3.625</v>
       </c>
       <c r="D2">
-        <v>-0.25</v>
+        <v>-0.375</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1175,10 +1251,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>2.5</v>
+        <v>2.625</v>
       </c>
       <c r="D3">
-        <v>-0.5</v>
+        <v>-0.375</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -1189,13 +1265,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>1.625</v>
+        <v>2.375</v>
       </c>
       <c r="D4">
-        <v>-0.375</v>
+        <v>0.375</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1209,10 +1285,10 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>1.375</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>0.375</v>
+        <v>1</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1223,16 +1299,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>1.375</v>
+        <v>1.625</v>
       </c>
       <c r="D6">
-        <v>0.375</v>
+        <v>-0.375</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1243,13 +1319,13 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>1.375</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>-0.625</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1257,16 +1333,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="D8">
-        <v>0.75</v>
+        <v>-0.75</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1274,16 +1350,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>0.625</v>
+        <v>1.125</v>
       </c>
       <c r="D9">
-        <v>-0.375</v>
+        <v>1.125</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1298,54 +1374,54 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2">
-        <v>64.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="C2">
-        <v>34</v>
+        <v>15.3</v>
       </c>
       <c r="D2">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="E2">
+        <v>0.3</v>
+      </c>
+      <c r="F2">
         <v>0.1</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1362,167 +1438,167 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>35.4</v>
+        <v>6.9</v>
       </c>
       <c r="C3">
-        <v>61</v>
+        <v>35.3</v>
       </c>
       <c r="D3">
-        <v>3.4</v>
+        <v>38.1</v>
       </c>
       <c r="E3">
-        <v>0.2</v>
+        <v>13.9</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B4">
-        <v>0.3</v>
+        <v>11.3</v>
       </c>
       <c r="C4">
-        <v>0.9</v>
+        <v>39.8</v>
       </c>
       <c r="D4">
-        <v>32.1</v>
+        <v>33.3</v>
       </c>
       <c r="E4">
-        <v>29.3</v>
+        <v>10.1</v>
       </c>
       <c r="F4">
-        <v>24.8</v>
+        <v>3.9</v>
       </c>
       <c r="G4">
-        <v>9.199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="H4">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="I4">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>96.59999999999999</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="C5">
-        <v>2.3</v>
+        <v>6.6</v>
       </c>
       <c r="D5">
-        <v>30.2</v>
+        <v>16.1</v>
       </c>
       <c r="E5">
-        <v>30.1</v>
+        <v>41</v>
       </c>
       <c r="F5">
-        <v>23.1</v>
+        <v>19.6</v>
       </c>
       <c r="G5">
-        <v>10.8</v>
+        <v>10.1</v>
       </c>
       <c r="H5">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="I5">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J5">
-        <v>96.59999999999999</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C6">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>27.5</v>
+        <v>4.9</v>
       </c>
       <c r="E6">
-        <v>27.3</v>
+        <v>17.7</v>
       </c>
       <c r="F6">
-        <v>26.9</v>
+        <v>30.9</v>
       </c>
       <c r="G6">
-        <v>12.6</v>
+        <v>27.1</v>
       </c>
       <c r="H6">
-        <v>3.5</v>
+        <v>13.4</v>
       </c>
       <c r="I6">
-        <v>0.4</v>
+        <v>3.9</v>
       </c>
       <c r="J6">
-        <v>96.09999999999999</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="E7">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="F7">
-        <v>19.3</v>
+        <v>24.9</v>
       </c>
       <c r="G7">
-        <v>41.2</v>
+        <v>31.7</v>
       </c>
       <c r="H7">
-        <v>17.7</v>
+        <v>19.9</v>
       </c>
       <c r="I7">
-        <v>6.4</v>
+        <v>8.9</v>
       </c>
       <c r="J7">
-        <v>75.90000000000001</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1531,25 +1607,25 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>1.2</v>
+        <v>5.4</v>
       </c>
       <c r="F8">
-        <v>3.6</v>
+        <v>12.6</v>
       </c>
       <c r="G8">
-        <v>14.4</v>
+        <v>19.4</v>
       </c>
       <c r="H8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I8">
-        <v>38.2</v>
+        <v>21.6</v>
       </c>
       <c r="J8">
-        <v>19.8</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1563,25 +1639,25 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E9">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="F9">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="G9">
-        <v>11.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H9">
-        <v>32.1</v>
+        <v>21.3</v>
       </c>
       <c r="I9">
-        <v>52.9</v>
+        <v>64.2</v>
       </c>
       <c r="J9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
     </row>
   </sheetData>
@@ -1591,26 +1667,29 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>31</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -1624,10 +1703,13 @@
       <c r="E2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3">
         <v>100</v>
@@ -1639,109 +1721,130 @@
         <v>100</v>
       </c>
       <c r="E3">
+        <v>99.8</v>
+      </c>
+      <c r="F3">
+        <v>99.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
         <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4">
-        <v>93.7</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4">
-        <v>98</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="E4">
-        <v>95.89999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>99.8</v>
+      </c>
+      <c r="F4">
+        <v>99.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5">
+        <v>93.7</v>
+      </c>
+      <c r="C5">
+        <v>100</v>
+      </c>
+      <c r="D5">
+        <v>97.8</v>
+      </c>
+      <c r="E5">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="F5">
+        <v>94.09999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>57.7</v>
+      </c>
+      <c r="C6">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="D6">
+        <v>75.8</v>
+      </c>
+      <c r="E6">
+        <v>77.3</v>
+      </c>
+      <c r="F6">
+        <v>79.40000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>2.2</v>
+      </c>
+      <c r="C7">
+        <v>11.4</v>
+      </c>
+      <c r="D7">
+        <v>23</v>
+      </c>
+      <c r="E7">
+        <v>75.7</v>
+      </c>
+      <c r="F7">
+        <v>69.09999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>93.2</v>
-      </c>
-      <c r="C5">
-        <v>91.7</v>
-      </c>
-      <c r="D5">
+      <c r="B8">
         <v>96.3</v>
       </c>
-      <c r="E5">
-        <v>95.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>100</v>
-      </c>
-      <c r="C6">
-        <v>100</v>
-      </c>
-      <c r="D6">
+      <c r="C8">
+        <v>92.30000000000001</v>
+      </c>
+      <c r="D8">
         <v>96.5</v>
       </c>
-      <c r="E6">
-        <v>95.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>62</v>
-      </c>
-      <c r="C7">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="D7">
-        <v>75.5</v>
-      </c>
-      <c r="E7">
-        <v>77.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>1.5</v>
-      </c>
-      <c r="C8">
-        <v>11.3</v>
-      </c>
-      <c r="D8">
-        <v>20.2</v>
-      </c>
       <c r="E8">
-        <v>20.9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>43.4</v>
+      </c>
+      <c r="F8">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B9">
-        <v>49.6</v>
+        <v>50.1</v>
       </c>
       <c r="C9">
-        <v>10.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D9">
-        <v>13.5</v>
+        <v>11.7</v>
       </c>
       <c r="E9">
-        <v>14.9</v>
+        <v>11.6</v>
+      </c>
+      <c r="F9">
+        <v>16.2</v>
       </c>
     </row>
   </sheetData>
@@ -1756,28 +1859,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1788,25 +1891,25 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D2">
-        <v>107.74</v>
+        <v>114.68</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>126.61</v>
+        <v>126.95</v>
       </c>
       <c r="G2">
-        <v>0.515</v>
+        <v>0.475</v>
       </c>
       <c r="H2">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1814,28 +1917,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3">
-        <v>117.23</v>
+        <v>108.92</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>125.75</v>
+        <v>127.96</v>
       </c>
       <c r="G3">
-        <v>0.515</v>
+        <v>0.525</v>
       </c>
       <c r="H3">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1843,28 +1946,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D4">
-        <v>126.7</v>
+        <v>116.51</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>124.88</v>
+        <v>124.3</v>
       </c>
       <c r="G4">
-        <v>0.515</v>
+        <v>0.45</v>
       </c>
       <c r="H4">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1872,28 +1975,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D5">
-        <v>108.78</v>
+        <v>133.56</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>125.81</v>
+        <v>125.31</v>
       </c>
       <c r="G5">
-        <v>0.545</v>
+        <v>0.5</v>
       </c>
       <c r="H5">
-        <v>0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1901,28 +2004,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D6">
-        <v>120.93</v>
+        <v>144.3</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>124.71</v>
+        <v>123.83</v>
       </c>
       <c r="G6">
-        <v>0.485</v>
+        <v>0.475</v>
       </c>
       <c r="H6">
-        <v>0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1930,28 +2033,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D7">
-        <v>143.31</v>
+        <v>110.53</v>
       </c>
       <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7">
+        <v>124.84</v>
+      </c>
+      <c r="G7">
+        <v>0.525</v>
+      </c>
+      <c r="H7">
+        <v>-1.5</v>
+      </c>
+      <c r="I7">
         <v>10</v>
-      </c>
-      <c r="F7">
-        <v>123.37</v>
-      </c>
-      <c r="G7">
-        <v>0.455</v>
-      </c>
-      <c r="H7">
-        <v>-0.8</v>
-      </c>
-      <c r="I7">
-        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1959,28 +2062,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D8">
-        <v>126.31</v>
+        <v>128.94</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8">
-        <v>124.22</v>
+        <v>122.28</v>
       </c>
       <c r="G8">
-        <v>0.515</v>
+        <v>0.5</v>
       </c>
       <c r="H8">
-        <v>-0.8</v>
+        <v>-1.8</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1988,28 +2091,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D9">
-        <v>146.71</v>
+        <v>141.31</v>
       </c>
       <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9">
+        <v>123.29</v>
+      </c>
+      <c r="G9">
+        <v>0.55</v>
+      </c>
+      <c r="H9">
+        <v>-2.5</v>
+      </c>
+      <c r="I9">
         <v>10</v>
-      </c>
-      <c r="F9">
-        <v>122.36</v>
-      </c>
-      <c r="G9">
-        <v>0.455</v>
-      </c>
-      <c r="H9">
-        <v>-1.9</v>
-      </c>
-      <c r="I9">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2024,48 +2127,48 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>146.7133333333333</v>
+        <v>144.3</v>
       </c>
       <c r="E2">
-        <v>440.14</v>
+        <v>577.2</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -2074,184 +2177,184 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D3">
-        <v>143.3133333333333</v>
+        <v>133.565</v>
       </c>
       <c r="E3">
-        <v>429.94</v>
+        <v>534.26</v>
       </c>
       <c r="F3">
-        <v>100</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C4">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D4">
-        <v>126.7</v>
+        <v>141.315</v>
       </c>
       <c r="E4">
-        <v>380.1</v>
+        <v>565.26</v>
       </c>
       <c r="F4">
-        <v>96.59999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="G4">
-        <v>0.8999999999999999</v>
+        <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C5">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="D5">
-        <v>126.3066666666667</v>
+        <v>128.945</v>
       </c>
       <c r="E5">
-        <v>378.92</v>
+        <v>515.78</v>
       </c>
       <c r="F5">
-        <v>96.59999999999999</v>
+        <v>94</v>
       </c>
       <c r="G5">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="H5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C6">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>120.9266666666667</v>
+        <v>116.51</v>
       </c>
       <c r="E6">
-        <v>362.78</v>
+        <v>466.04</v>
       </c>
       <c r="F6">
-        <v>96.09999999999999</v>
+        <v>82.69999999999999</v>
       </c>
       <c r="G6">
-        <v>0.4</v>
+        <v>3.9</v>
       </c>
       <c r="H6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I6" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C7">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>117.2266666666667</v>
+        <v>114.68</v>
       </c>
       <c r="E7">
-        <v>351.68</v>
+        <v>458.72</v>
       </c>
       <c r="F7">
-        <v>75.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="G7">
-        <v>6.4</v>
+        <v>8.9</v>
       </c>
       <c r="H7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C8">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D8">
-        <v>107.74</v>
+        <v>108.92</v>
       </c>
       <c r="E8">
-        <v>323.22</v>
+        <v>435.6800000000001</v>
       </c>
       <c r="F8">
-        <v>19.8</v>
+        <v>38.4</v>
       </c>
       <c r="G8">
-        <v>38.2</v>
+        <v>21.6</v>
       </c>
       <c r="H8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="I8" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2259,28 +2362,28 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>108.78</v>
+        <v>110.53</v>
       </c>
       <c r="E9">
-        <v>326.34</v>
+        <v>442.12</v>
       </c>
       <c r="F9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="G9">
-        <v>52.90000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="H9" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2295,19 +2398,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2315,19 +2418,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2335,19 +2438,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D3">
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2355,19 +2458,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2378,16 +2481,16 @@
         <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2398,16 +2501,16 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D6">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2415,19 +2518,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D7">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2435,19 +2538,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
         <v>41</v>
       </c>
       <c r="D8">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2458,16 +2561,16 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D9">
-        <v>-16</v>
+        <v>-20</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -2477,75 +2580,87 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>8</v>
+      </c>
+      <c r="D2">
+        <v>14</v>
+      </c>
+      <c r="E2">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>8</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>12</v>
+      </c>
+      <c r="D4">
+        <v>16</v>
+      </c>
+      <c r="E4">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>12</v>
-      </c>
-      <c r="D2">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>8</v>
-      </c>
-      <c r="D3">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>8</v>
-      </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="E4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -2558,11 +2673,14 @@
       <c r="D5">
         <v>0</v>
       </c>
-      <c r="E5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -2575,45 +2693,54 @@
       <c r="D6">
         <v>-3</v>
       </c>
-      <c r="E6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="E6">
+        <v>-8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>-10</v>
+      </c>
+      <c r="D7">
+        <v>-9</v>
+      </c>
+      <c r="E7">
+        <v>-8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>2</v>
       </c>
-      <c r="C7">
+      <c r="C8">
         <v>-6</v>
       </c>
-      <c r="D7">
+      <c r="D8">
         <v>-6</v>
       </c>
-      <c r="E7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>-10</v>
-      </c>
-      <c r="D8">
-        <v>-9</v>
-      </c>
-      <c r="E8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="E8">
+        <v>-12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -2626,8 +2753,11 @@
       <c r="D9">
         <v>-16</v>
       </c>
-      <c r="E9" t="s">
-        <v>74</v>
+      <c r="E9">
+        <v>-20</v>
+      </c>
+      <c r="F9" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/EBC League 2026.xlsx
+++ b/data/leagues/EBC League 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="96">
   <si>
     <t>P90 Asiimov</t>
   </si>
@@ -49,19 +49,22 @@
     <t xml:space="preserve">First down syndrome </t>
   </si>
   <si>
-    <t>1-3-0</t>
-  </si>
-  <si>
-    <t>2-2-0</t>
-  </si>
-  <si>
-    <t>3-1-0</t>
-  </si>
-  <si>
-    <t>0-4-0</t>
-  </si>
-  <si>
-    <t>4-0-0</t>
+    <t>1-4-0</t>
+  </si>
+  <si>
+    <t>2-3-0</t>
+  </si>
+  <si>
+    <t>3-2-0</t>
+  </si>
+  <si>
+    <t>4-1-0</t>
+  </si>
+  <si>
+    <t>0-5-0</t>
+  </si>
+  <si>
+    <t>5-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -124,6 +127,9 @@
     <t>Week_5</t>
   </si>
   <si>
+    <t>Week_6</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -145,30 +151,30 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Alina Wise</t>
+  </si>
+  <si>
     <t>Jackson Jansorn</t>
   </si>
   <si>
-    <t>Alina Wise</t>
-  </si>
-  <si>
     <t>Kate Zacierka</t>
   </si>
   <si>
+    <t>Derek Alcavage</t>
+  </si>
+  <si>
+    <t>Louis Rodriguez</t>
+  </si>
+  <si>
+    <t>jack meehan</t>
+  </si>
+  <si>
     <t>Gianpierre Lopez</t>
   </si>
   <si>
-    <t>jack meehan</t>
-  </si>
-  <si>
     <t>Mike Zacierka</t>
   </si>
   <si>
-    <t>Louis Rodriguez</t>
-  </si>
-  <si>
-    <t>Derek Alcavage</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -193,46 +199,43 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>4-0</t>
-  </si>
-  <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>0-4</t>
-  </si>
-  <si>
-    <t>11.5-2.4-0.1</t>
-  </si>
-  <si>
-    <t>8.9-5.0-0.1</t>
-  </si>
-  <si>
-    <t>8.9-5.1-0.1</t>
-  </si>
-  <si>
-    <t>6.8-7.1-0.1</t>
-  </si>
-  <si>
-    <t>6.0-7.9-0.1</t>
-  </si>
-  <si>
-    <t>5.5-8.4-0.1</t>
-  </si>
-  <si>
-    <t>4.8-9.1-0.1</t>
-  </si>
-  <si>
-    <t>3.2-10.7-0.1</t>
-  </si>
-  <si>
-    <t>12-2</t>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>10.2-3.7-0.1</t>
+  </si>
+  <si>
+    <t>9.9-4.0-0.1</t>
+  </si>
+  <si>
+    <t>8.8-5.1-0.1</t>
+  </si>
+  <si>
+    <t>6.7-7.1-0.1</t>
+  </si>
+  <si>
+    <t>5.7-8.2-0.1</t>
+  </si>
+  <si>
+    <t>5.4-8.5-0.1</t>
+  </si>
+  <si>
+    <t>4.6-9.3-0.1</t>
+  </si>
+  <si>
+    <t>4.3-9.6-0.1</t>
+  </si>
+  <si>
+    <t>10-4</t>
   </si>
   <si>
     <t>9-5</t>
@@ -244,10 +247,7 @@
     <t>6-8</t>
   </si>
   <si>
-    <t>5-9</t>
-  </si>
-  <si>
-    <t>3-11</t>
+    <t>4-10</t>
   </si>
   <si>
     <t>Owners</t>
@@ -259,30 +259,24 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑4</t>
-  </si>
-  <si>
-    <t>↑10</t>
-  </si>
-  <si>
-    <t>↓7</t>
+    <t>0</t>
+  </si>
+  <si>
+    <t>↑3</t>
+  </si>
+  <si>
+    <t>↓4</t>
   </si>
   <si>
     <t>↑6</t>
   </si>
   <si>
-    <t>↓5</t>
-  </si>
-  <si>
-    <t>↑1</t>
+    <t>↓3</t>
   </si>
   <si>
     <t>↓6</t>
   </si>
   <si>
-    <t>↓4</t>
-  </si>
-  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -293,6 +287,9 @@
   </si>
   <si>
     <t>Week 4</t>
+  </si>
+  <si>
+    <t>Week 5</t>
   </si>
   <si>
     <t>Week</t>
@@ -711,13 +708,13 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
         <v>10</v>
@@ -726,7 +723,7 @@
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -734,28 +731,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>10</v>
-      </c>
-      <c r="I3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -766,25 +763,25 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" t="s">
         <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -795,25 +792,25 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -824,25 +821,25 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
         <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>9</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6" t="s">
         <v>10</v>
       </c>
       <c r="H6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -862,7 +859,7 @@
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7" t="s">
         <v>9</v>
@@ -891,7 +888,7 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>10</v>
@@ -911,25 +908,25 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" t="s">
         <v>11</v>
       </c>
-      <c r="G9" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>10</v>
-      </c>
-      <c r="I9" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -939,30 +936,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1022,25 +1019,25 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="F4">
-        <v>-6</v>
+        <v>9</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1048,25 +1045,77 @@
         <v>3</v>
       </c>
       <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
         <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
       </c>
       <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>-6</v>
+      </c>
+      <c r="G5">
+        <v>10</v>
+      </c>
+      <c r="H5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6">
         <v>-20</v>
       </c>
-      <c r="F5">
+      <c r="F6">
         <v>-12</v>
       </c>
-      <c r="G5">
-        <v>8</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>12</v>
+      </c>
+      <c r="F7">
+        <v>18</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+      <c r="H7" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1081,13 +1130,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1095,13 +1144,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>1.25</v>
+        <v>1.625</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1109,13 +1158,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>1.5</v>
+        <v>2.125</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1126,10 +1175,10 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1137,13 +1186,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>1.875</v>
+        <v>2.375</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1151,13 +1200,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1165,13 +1214,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>2.125</v>
+        <v>2.75</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1182,7 +1231,7 @@
         <v>5</v>
       </c>
       <c r="C8">
-        <v>2.625</v>
+        <v>3</v>
       </c>
       <c r="D8" t="s">
         <v>9</v>
@@ -1196,7 +1245,7 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>2.875</v>
+        <v>3.375</v>
       </c>
       <c r="D9" t="s">
         <v>9</v>
@@ -1214,16 +1263,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1234,13 +1283,13 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>3.625</v>
+        <v>3.875</v>
       </c>
       <c r="D2">
-        <v>-0.375</v>
+        <v>-0.125</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1251,13 +1300,13 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>2.625</v>
+        <v>3.5</v>
       </c>
       <c r="D3">
-        <v>-0.375</v>
+        <v>-0.5</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1268,13 +1317,13 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>2.375</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1285,10 +1334,10 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>2.375</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>1.375</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1299,16 +1348,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>1.625</v>
+        <v>2.125</v>
       </c>
       <c r="D6">
-        <v>-0.375</v>
+        <v>-0.875</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1316,16 +1365,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>1.375</v>
+        <v>2.125</v>
       </c>
       <c r="D7">
-        <v>-0.625</v>
+        <v>1.125</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1333,13 +1382,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="D8">
-        <v>-0.75</v>
+        <v>-0.25</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1350,16 +1399,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>1.125</v>
+        <v>1.25</v>
       </c>
       <c r="D9">
-        <v>1.125</v>
+        <v>-0.75</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1374,57 +1423,57 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2">
-        <v>81.09999999999999</v>
+        <v>45.3</v>
       </c>
       <c r="C2">
-        <v>15.3</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>3.2</v>
+        <v>16.3</v>
       </c>
       <c r="E2">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
       <c r="F2">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1438,34 +1487,34 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3">
-        <v>6.9</v>
+        <v>34.6</v>
       </c>
       <c r="C3">
-        <v>35.3</v>
+        <v>35.8</v>
       </c>
       <c r="D3">
-        <v>38.1</v>
+        <v>24.1</v>
       </c>
       <c r="E3">
-        <v>13.9</v>
+        <v>4.6</v>
       </c>
       <c r="F3">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="G3">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="H3">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1473,132 +1522,132 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>11.3</v>
+        <v>19.1</v>
       </c>
       <c r="C4">
-        <v>39.8</v>
+        <v>27.5</v>
       </c>
       <c r="D4">
-        <v>33.3</v>
+        <v>38.4</v>
       </c>
       <c r="E4">
-        <v>10.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F4">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="G4">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="H4">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>99.59999999999999</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B5">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="C5">
-        <v>6.6</v>
+        <v>2.1</v>
       </c>
       <c r="D5">
-        <v>16.1</v>
+        <v>12.1</v>
       </c>
       <c r="E5">
-        <v>41</v>
+        <v>34.4</v>
       </c>
       <c r="F5">
-        <v>19.6</v>
+        <v>26.4</v>
       </c>
       <c r="G5">
-        <v>10.1</v>
+        <v>16.5</v>
       </c>
       <c r="H5">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="I5">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>94</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B6">
         <v>0.1</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="D6">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="E6">
-        <v>17.7</v>
+        <v>23.2</v>
       </c>
       <c r="F6">
-        <v>30.9</v>
+        <v>27.9</v>
       </c>
       <c r="G6">
-        <v>27.1</v>
+        <v>23.4</v>
       </c>
       <c r="H6">
-        <v>13.4</v>
+        <v>11.8</v>
       </c>
       <c r="I6">
-        <v>3.9</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
-        <v>82.7</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="D7">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="E7">
-        <v>10.4</v>
+        <v>17.9</v>
       </c>
       <c r="F7">
-        <v>24.9</v>
+        <v>20.1</v>
       </c>
       <c r="G7">
-        <v>31.7</v>
+        <v>27.5</v>
       </c>
       <c r="H7">
-        <v>19.9</v>
+        <v>18.3</v>
       </c>
       <c r="I7">
-        <v>8.9</v>
+        <v>12.2</v>
       </c>
       <c r="J7">
-        <v>71.2</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1607,30 +1656,30 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="E8">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="F8">
-        <v>12.6</v>
+        <v>11.9</v>
       </c>
       <c r="G8">
-        <v>19.4</v>
+        <v>18.4</v>
       </c>
       <c r="H8">
-        <v>40</v>
+        <v>33.7</v>
       </c>
       <c r="I8">
-        <v>21.6</v>
+        <v>31.5</v>
       </c>
       <c r="J8">
-        <v>38.4</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1639,25 +1688,25 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E9">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="F9">
-        <v>3.8</v>
+        <v>8.5</v>
       </c>
       <c r="G9">
-        <v>9.300000000000001</v>
+        <v>12.4</v>
       </c>
       <c r="H9">
-        <v>21.3</v>
+        <v>30.2</v>
       </c>
       <c r="I9">
-        <v>64.2</v>
+        <v>45.7</v>
       </c>
       <c r="J9">
-        <v>14.5</v>
+        <v>24.1</v>
       </c>
     </row>
   </sheetData>
@@ -1667,29 +1716,32 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>33</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -1701,15 +1753,18 @@
         <v>100</v>
       </c>
       <c r="E2">
+        <v>99.7</v>
+      </c>
+      <c r="F2">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="G2">
         <v>100</v>
       </c>
-      <c r="F2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3">
         <v>100</v>
@@ -1721,13 +1776,16 @@
         <v>100</v>
       </c>
       <c r="E3">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="F3">
-        <v>99.8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="G3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1738,113 +1796,131 @@
         <v>100</v>
       </c>
       <c r="D4">
-        <v>95.19999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="E4">
         <v>99.8</v>
       </c>
       <c r="F4">
-        <v>99.7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="G4">
+        <v>99.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B5">
-        <v>93.7</v>
+        <v>56.99999999999999</v>
       </c>
       <c r="C5">
+        <v>84.2</v>
+      </c>
+      <c r="D5">
+        <v>73.7</v>
+      </c>
+      <c r="E5">
+        <v>82</v>
+      </c>
+      <c r="F5">
+        <v>93.60000000000001</v>
+      </c>
+      <c r="G5">
+        <v>89.90000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="C6">
         <v>100</v>
       </c>
-      <c r="D5">
-        <v>97.8</v>
-      </c>
-      <c r="E5">
+      <c r="D6">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="E6">
+        <v>91.8</v>
+      </c>
+      <c r="F6">
+        <v>79.60000000000001</v>
+      </c>
+      <c r="G6">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>53.6</v>
+      </c>
+      <c r="C7">
+        <v>12.4</v>
+      </c>
+      <c r="D7">
+        <v>15.1</v>
+      </c>
+      <c r="E7">
+        <v>12.1</v>
+      </c>
+      <c r="F7">
+        <v>70.8</v>
+      </c>
+      <c r="G7">
+        <v>73.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>1.9</v>
+      </c>
+      <c r="C8">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="F8">
+        <v>29.7</v>
+      </c>
+      <c r="G8">
+        <v>32.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="C9">
         <v>92.40000000000001</v>
       </c>
-      <c r="F5">
-        <v>94.09999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6">
-        <v>57.7</v>
-      </c>
-      <c r="C6">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="D6">
-        <v>75.8</v>
-      </c>
-      <c r="E6">
-        <v>77.3</v>
-      </c>
-      <c r="F6">
-        <v>79.40000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>2.2</v>
-      </c>
-      <c r="C7">
-        <v>11.4</v>
-      </c>
-      <c r="D7">
-        <v>23</v>
-      </c>
-      <c r="E7">
-        <v>75.7</v>
-      </c>
-      <c r="F7">
-        <v>69.09999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8">
-        <v>96.3</v>
-      </c>
-      <c r="C8">
-        <v>92.30000000000001</v>
-      </c>
-      <c r="D8">
-        <v>96.5</v>
-      </c>
-      <c r="E8">
-        <v>43.4</v>
-      </c>
-      <c r="F8">
-        <v>41.7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9">
-        <v>50.1</v>
-      </c>
-      <c r="C9">
-        <v>9.199999999999999</v>
-      </c>
       <c r="D9">
-        <v>11.7</v>
+        <v>97</v>
       </c>
       <c r="E9">
-        <v>11.6</v>
+        <v>41.2</v>
       </c>
       <c r="F9">
-        <v>16.2</v>
+        <v>26.6</v>
+      </c>
+      <c r="G9">
+        <v>22.7</v>
       </c>
     </row>
   </sheetData>
@@ -1859,28 +1935,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1888,28 +1964,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D2">
-        <v>114.68</v>
+        <v>108.55</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2">
-        <v>126.95</v>
+        <v>129.52</v>
       </c>
       <c r="G2">
-        <v>0.475</v>
+        <v>0.511</v>
       </c>
       <c r="H2">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1917,28 +1993,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D3">
-        <v>108.92</v>
+        <v>111.65</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3">
-        <v>127.96</v>
+        <v>129</v>
       </c>
       <c r="G3">
-        <v>0.525</v>
+        <v>0.511</v>
       </c>
       <c r="H3">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1949,25 +2025,25 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D4">
-        <v>116.51</v>
+        <v>121.76</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>124.3</v>
+        <v>127.98</v>
       </c>
       <c r="G4">
-        <v>0.45</v>
+        <v>0.467</v>
       </c>
       <c r="H4">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1975,28 +2051,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D5">
-        <v>133.56</v>
+        <v>139.86</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5">
-        <v>125.31</v>
+        <v>125.4</v>
       </c>
       <c r="G5">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="H5">
-        <v>-0.6</v>
+        <v>-0.2</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2004,28 +2080,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D6">
-        <v>144.3</v>
+        <v>127.53</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>123.83</v>
+        <v>125.5</v>
       </c>
       <c r="G6">
-        <v>0.475</v>
+        <v>0.556</v>
       </c>
       <c r="H6">
-        <v>-0.8</v>
+        <v>-1.6</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2033,28 +2109,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D7">
-        <v>110.53</v>
+        <v>137.15</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7">
-        <v>124.84</v>
+        <v>124.54</v>
       </c>
       <c r="G7">
-        <v>0.525</v>
+        <v>0.467</v>
       </c>
       <c r="H7">
-        <v>-1.5</v>
+        <v>-2.8</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2062,28 +2138,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8">
-        <v>128.94</v>
+        <v>138.91</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F8">
-        <v>122.28</v>
+        <v>123.31</v>
       </c>
       <c r="G8">
-        <v>0.5</v>
+        <v>0.422</v>
       </c>
       <c r="H8">
-        <v>-1.8</v>
+        <v>-3.4</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2091,28 +2167,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D9">
-        <v>141.31</v>
+        <v>124.15</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9">
-        <v>123.29</v>
+        <v>124.31</v>
       </c>
       <c r="G9">
-        <v>0.55</v>
+        <v>0.533</v>
       </c>
       <c r="H9">
-        <v>-2.5</v>
+        <v>-3.8</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -2127,48 +2203,48 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D2">
-        <v>144.3</v>
+        <v>138.912</v>
       </c>
       <c r="E2">
-        <v>577.2</v>
+        <v>694.5599999999999</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -2177,36 +2253,36 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C3">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D3">
-        <v>133.565</v>
+        <v>137.148</v>
       </c>
       <c r="E3">
-        <v>534.26</v>
+        <v>685.74</v>
       </c>
       <c r="F3">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I3" t="s">
         <v>70</v>
@@ -2217,170 +2293,170 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C4">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D4">
-        <v>141.315</v>
+        <v>139.86</v>
       </c>
       <c r="E4">
-        <v>565.26</v>
+        <v>699.3</v>
       </c>
       <c r="F4">
-        <v>99.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
       </c>
       <c r="C5">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="D5">
-        <v>128.945</v>
+        <v>121.756</v>
       </c>
       <c r="E5">
-        <v>515.78</v>
+        <v>608.78</v>
       </c>
       <c r="F5">
-        <v>94</v>
+        <v>92.30000000000001</v>
       </c>
       <c r="G5">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D6">
-        <v>116.51</v>
+        <v>127.528</v>
       </c>
       <c r="E6">
-        <v>466.04</v>
+        <v>637.64</v>
       </c>
       <c r="F6">
-        <v>82.69999999999999</v>
+        <v>79.60000000000001</v>
       </c>
       <c r="G6">
-        <v>3.9</v>
+        <v>8.6</v>
       </c>
       <c r="H6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D7">
-        <v>114.68</v>
+        <v>124.152</v>
       </c>
       <c r="E7">
-        <v>458.72</v>
+        <v>620.76</v>
       </c>
       <c r="F7">
-        <v>71.2</v>
+        <v>69.5</v>
       </c>
       <c r="G7">
-        <v>8.9</v>
+        <v>12.2</v>
       </c>
       <c r="H7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D8">
-        <v>108.92</v>
+        <v>111.652</v>
       </c>
       <c r="E8">
-        <v>435.6800000000001</v>
+        <v>558.26</v>
       </c>
       <c r="F8">
-        <v>38.4</v>
+        <v>34.8</v>
       </c>
       <c r="G8">
-        <v>21.6</v>
+        <v>31.5</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D9">
-        <v>110.53</v>
+        <v>108.552</v>
       </c>
       <c r="E9">
-        <v>442.12</v>
+        <v>542.7600000000001</v>
       </c>
       <c r="F9">
-        <v>14.5</v>
+        <v>24.1</v>
       </c>
       <c r="G9">
-        <v>64.2</v>
+        <v>45.7</v>
       </c>
       <c r="H9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I9" t="s">
         <v>74</v>
@@ -2398,7 +2474,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>75</v>
@@ -2407,7 +2483,7 @@
         <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>77</v>
@@ -2421,13 +2497,13 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D2">
         <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
         <v>78</v>
@@ -2438,16 +2514,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>79</v>
@@ -2458,13 +2534,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -2484,13 +2560,13 @@
         <v>46</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2498,19 +2574,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D6">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2518,19 +2594,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7">
         <v>-8</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2541,16 +2617,16 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2561,16 +2637,16 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D9">
-        <v>-20</v>
+        <v>-26</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -2580,27 +2656,30 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -2616,51 +2695,60 @@
       <c r="E2">
         <v>18</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
         <v>4</v>
       </c>
-      <c r="B3">
+      <c r="C3">
+        <v>12</v>
+      </c>
+      <c r="D3">
+        <v>16</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
         <v>3</v>
       </c>
-      <c r="C3">
-        <v>8</v>
-      </c>
-      <c r="D3">
+      <c r="C4">
+        <v>8</v>
+      </c>
+      <c r="D4">
         <v>4</v>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>14</v>
       </c>
-      <c r="F3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="C4">
-        <v>12</v>
-      </c>
-      <c r="D4">
-        <v>16</v>
-      </c>
-      <c r="E4">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="F4">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -2676,51 +2764,60 @@
       <c r="E5">
         <v>6</v>
       </c>
-      <c r="F5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B6">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="D6">
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="E6">
         <v>-8</v>
       </c>
-      <c r="F6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="F6">
+        <v>-2</v>
+      </c>
+      <c r="G6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="C7">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="D7">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="E7">
         <v>-8</v>
       </c>
-      <c r="F7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="F7">
+        <v>-8</v>
+      </c>
+      <c r="G7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -2736,11 +2833,14 @@
       <c r="E8">
         <v>-12</v>
       </c>
-      <c r="F8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="F8">
+        <v>-15</v>
+      </c>
+      <c r="G8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -2756,8 +2856,11 @@
       <c r="E9">
         <v>-20</v>
       </c>
-      <c r="F9" t="s">
-        <v>85</v>
+      <c r="F9">
+        <v>-26</v>
+      </c>
+      <c r="G9" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/EBC League 2026.xlsx
+++ b/data/leagues/EBC League 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="99">
   <si>
     <t>P90 Asiimov</t>
   </si>
@@ -49,22 +49,25 @@
     <t xml:space="preserve">First down syndrome </t>
   </si>
   <si>
-    <t>1-4-0</t>
-  </si>
-  <si>
-    <t>2-3-0</t>
-  </si>
-  <si>
-    <t>3-2-0</t>
-  </si>
-  <si>
-    <t>4-1-0</t>
-  </si>
-  <si>
-    <t>0-5-0</t>
-  </si>
-  <si>
-    <t>5-0-0</t>
+    <t>2-4-0</t>
+  </si>
+  <si>
+    <t>3-3-0</t>
+  </si>
+  <si>
+    <t>1-5-0</t>
+  </si>
+  <si>
+    <t>4-2-0</t>
+  </si>
+  <si>
+    <t>5-1-0</t>
+  </si>
+  <si>
+    <t>0-6-0</t>
+  </si>
+  <si>
+    <t>6-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -130,6 +133,9 @@
     <t>Week_6</t>
   </si>
   <si>
+    <t>Week_7</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -151,30 +157,30 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Jackson Jansorn</t>
+  </si>
+  <si>
     <t>Alina Wise</t>
   </si>
   <si>
-    <t>Jackson Jansorn</t>
+    <t>jack meehan</t>
   </si>
   <si>
     <t>Kate Zacierka</t>
   </si>
   <si>
+    <t>Mike Zacierka</t>
+  </si>
+  <si>
     <t>Derek Alcavage</t>
   </si>
   <si>
     <t>Louis Rodriguez</t>
   </si>
   <si>
-    <t>jack meehan</t>
-  </si>
-  <si>
     <t>Gianpierre Lopez</t>
   </si>
   <si>
-    <t>Mike Zacierka</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -199,48 +205,45 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>10.2-3.7-0.1</t>
-  </si>
-  <si>
-    <t>9.9-4.0-0.1</t>
-  </si>
-  <si>
-    <t>8.8-5.1-0.1</t>
-  </si>
-  <si>
-    <t>6.7-7.1-0.1</t>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>9.3-4.7-0.1</t>
+  </si>
+  <si>
+    <t>9.4-4.5-0.1</t>
+  </si>
+  <si>
+    <t>9.8-4.1-0.1</t>
+  </si>
+  <si>
+    <t>6.6-7.3-0.1</t>
+  </si>
+  <si>
+    <t>6.4-7.5-0.1</t>
   </si>
   <si>
     <t>5.7-8.2-0.1</t>
   </si>
   <si>
-    <t>5.4-8.5-0.1</t>
-  </si>
-  <si>
-    <t>4.6-9.3-0.1</t>
-  </si>
-  <si>
-    <t>4.3-9.6-0.1</t>
+    <t>4.4-9.6-0.1</t>
+  </si>
+  <si>
+    <t>4.2-9.8-0.1</t>
   </si>
   <si>
     <t>10-4</t>
   </si>
   <si>
-    <t>9-5</t>
-  </si>
-  <si>
     <t>7-7</t>
   </si>
   <si>
@@ -259,24 +262,27 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>↑3</t>
+    <t>↑4</t>
+  </si>
+  <si>
+    <t>↑6</t>
+  </si>
+  <si>
+    <t>↑7</t>
+  </si>
+  <si>
+    <t>↓6</t>
+  </si>
+  <si>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>↓9</t>
   </si>
   <si>
     <t>↓4</t>
   </si>
   <si>
-    <t>↑6</t>
-  </si>
-  <si>
-    <t>↓3</t>
-  </si>
-  <si>
-    <t>↓6</t>
-  </si>
-  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -290,6 +296,9 @@
   </si>
   <si>
     <t>Week 5</t>
+  </si>
+  <si>
+    <t>Week 6</t>
   </si>
   <si>
     <t>Week</t>
@@ -708,7 +717,7 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -717,10 +726,10 @@
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I2" t="s">
         <v>11</v>
@@ -731,13 +740,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -749,10 +758,10 @@
         <v>9</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -760,28 +769,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
       <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
         <v>11</v>
       </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -789,22 +798,22 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
         <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
@@ -821,25 +830,25 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
         <v>11</v>
       </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -847,28 +856,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
         <v>9</v>
       </c>
-      <c r="D7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I7" t="s">
         <v>10</v>
-      </c>
-      <c r="G7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -876,28 +885,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" t="s">
         <v>10</v>
-      </c>
-      <c r="H8" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -905,28 +914,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
       </c>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -941,25 +950,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1130,13 +1139,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1147,7 +1156,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1.625</v>
+        <v>1.875</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -1161,10 +1170,10 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>2.125</v>
+        <v>2.625</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1172,13 +1181,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1186,13 +1195,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>2.375</v>
+        <v>2.875</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1200,13 +1209,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1214,13 +1223,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1231,10 +1240,10 @@
         <v>5</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="D8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1245,10 +1254,10 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>3.375</v>
+        <v>3.875</v>
       </c>
       <c r="D9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1263,16 +1272,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1283,13 +1292,13 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>3.875</v>
+        <v>4.25</v>
       </c>
       <c r="D2">
-        <v>-0.125</v>
+        <v>-0.75</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1300,10 +1309,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>4.125</v>
       </c>
       <c r="D3">
-        <v>-0.5</v>
+        <v>0.125</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -1317,13 +1326,13 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1334,10 +1343,10 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>2.375</v>
+        <v>3.25</v>
       </c>
       <c r="D5">
-        <v>1.375</v>
+        <v>1.25</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1348,16 +1357,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>2.125</v>
+        <v>2.75</v>
       </c>
       <c r="D6">
-        <v>-0.875</v>
+        <v>0.75</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1365,16 +1374,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>2.125</v>
+        <v>2.5</v>
       </c>
       <c r="D7">
-        <v>1.125</v>
+        <v>-0.5</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1391,7 +1400,7 @@
         <v>-0.25</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1402,13 +1411,13 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>1.25</v>
+        <v>1.375</v>
       </c>
       <c r="D9">
-        <v>-0.75</v>
+        <v>-0.625</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1423,34 +1432,34 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -1458,22 +1467,22 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>45.3</v>
+        <v>22.9</v>
       </c>
       <c r="C2">
-        <v>34</v>
+        <v>37.2</v>
       </c>
       <c r="D2">
-        <v>16.3</v>
+        <v>29.3</v>
       </c>
       <c r="E2">
-        <v>3.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F2">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="G2">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1490,22 +1499,22 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>34.6</v>
+        <v>24</v>
       </c>
       <c r="C3">
-        <v>35.8</v>
+        <v>30.1</v>
       </c>
       <c r="D3">
-        <v>24.1</v>
+        <v>33.9</v>
       </c>
       <c r="E3">
-        <v>4.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F3">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="G3">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1522,95 +1531,95 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>19.1</v>
+        <v>52.8</v>
       </c>
       <c r="C4">
         <v>27.5</v>
       </c>
       <c r="D4">
-        <v>38.4</v>
+        <v>15.2</v>
       </c>
       <c r="E4">
-        <v>9.300000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="F4">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="G4">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="H4">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>99.7</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="D5">
-        <v>12.1</v>
+        <v>10.9</v>
       </c>
       <c r="E5">
-        <v>34.4</v>
+        <v>36.3</v>
       </c>
       <c r="F5">
-        <v>26.4</v>
+        <v>27.4</v>
       </c>
       <c r="G5">
-        <v>16.5</v>
+        <v>13.3</v>
       </c>
       <c r="H5">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J5">
-        <v>92.3</v>
+        <v>91.59999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B6">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="C6">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="D6">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="E6">
-        <v>23.2</v>
+        <v>23.7</v>
       </c>
       <c r="F6">
-        <v>27.9</v>
+        <v>30.6</v>
       </c>
       <c r="G6">
-        <v>23.4</v>
+        <v>25</v>
       </c>
       <c r="H6">
-        <v>11.8</v>
+        <v>9.9</v>
       </c>
       <c r="I6">
-        <v>8.6</v>
+        <v>2.6</v>
       </c>
       <c r="J6">
-        <v>79.59999999999999</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1618,31 +1627,31 @@
         <v>1</v>
       </c>
       <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <v>0.1</v>
-      </c>
-      <c r="C7">
-        <v>0.2</v>
       </c>
       <c r="D7">
         <v>3.7</v>
       </c>
       <c r="E7">
-        <v>17.9</v>
+        <v>16.5</v>
       </c>
       <c r="F7">
-        <v>20.1</v>
+        <v>24.5</v>
       </c>
       <c r="G7">
-        <v>27.5</v>
+        <v>33.3</v>
       </c>
       <c r="H7">
-        <v>18.3</v>
+        <v>16</v>
       </c>
       <c r="I7">
-        <v>12.2</v>
+        <v>5.9</v>
       </c>
       <c r="J7">
-        <v>69.5</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1659,22 +1668,22 @@
         <v>0.3</v>
       </c>
       <c r="E8">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>11.9</v>
+        <v>7.2</v>
       </c>
       <c r="G8">
-        <v>18.4</v>
+        <v>14.8</v>
       </c>
       <c r="H8">
-        <v>33.7</v>
+        <v>38.6</v>
       </c>
       <c r="I8">
-        <v>31.5</v>
+        <v>37.1</v>
       </c>
       <c r="J8">
-        <v>34.8</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1688,25 +1697,25 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E9">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="F9">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="G9">
-        <v>12.4</v>
+        <v>12</v>
       </c>
       <c r="H9">
-        <v>30.2</v>
+        <v>29.8</v>
       </c>
       <c r="I9">
-        <v>45.7</v>
+        <v>51.6</v>
       </c>
       <c r="J9">
-        <v>24.1</v>
+        <v>18.6</v>
       </c>
     </row>
   </sheetData>
@@ -1716,30 +1725,33 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>35</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1753,16 +1765,19 @@
         <v>100</v>
       </c>
       <c r="E2">
-        <v>99.7</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G2">
+        <v>99.8</v>
+      </c>
+      <c r="H2">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1784,8 +1799,11 @@
       <c r="G3">
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="H3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1796,131 +1814,149 @@
         <v>100</v>
       </c>
       <c r="D4">
-        <v>96.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="E4">
-        <v>99.8</v>
+        <v>99.7</v>
       </c>
       <c r="F4">
-        <v>99.90000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="G4">
-        <v>99.8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5">
+        <v>93.89999999999999</v>
+      </c>
+      <c r="C5">
+        <v>100</v>
+      </c>
+      <c r="D5">
+        <v>97.8</v>
+      </c>
+      <c r="E5">
+        <v>94.5</v>
+      </c>
+      <c r="F5">
+        <v>81.69999999999999</v>
+      </c>
+      <c r="G5">
+        <v>91.7</v>
+      </c>
+      <c r="H5">
+        <v>93.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5">
-        <v>56.99999999999999</v>
-      </c>
-      <c r="C5">
-        <v>84.2</v>
-      </c>
-      <c r="D5">
-        <v>73.7</v>
-      </c>
-      <c r="E5">
-        <v>82</v>
-      </c>
-      <c r="F5">
-        <v>93.60000000000001</v>
-      </c>
-      <c r="G5">
-        <v>89.90000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="B6">
-        <v>94.09999999999999</v>
+        <v>59.9</v>
       </c>
       <c r="C6">
-        <v>100</v>
+        <v>84.89999999999999</v>
       </c>
       <c r="D6">
-        <v>97.09999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E6">
-        <v>91.8</v>
+        <v>78.5</v>
       </c>
       <c r="F6">
-        <v>79.60000000000001</v>
+        <v>93</v>
       </c>
       <c r="G6">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>85.8</v>
+      </c>
+      <c r="H6">
+        <v>90.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B7">
-        <v>53.6</v>
+        <v>49.6</v>
       </c>
       <c r="C7">
-        <v>12.4</v>
+        <v>10.4</v>
       </c>
       <c r="D7">
-        <v>15.1</v>
+        <v>14.8</v>
       </c>
       <c r="E7">
-        <v>12.1</v>
+        <v>10.5</v>
       </c>
       <c r="F7">
         <v>70.8</v>
       </c>
       <c r="G7">
-        <v>73.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>82.89999999999999</v>
+      </c>
+      <c r="H7">
+        <v>77.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B8">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="C8">
-        <v>11</v>
+        <v>12.2</v>
       </c>
       <c r="D8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F8">
-        <v>29.7</v>
+        <v>30.9</v>
       </c>
       <c r="G8">
-        <v>32.9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>22.8</v>
+      </c>
+      <c r="H8">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B9">
-        <v>93.40000000000001</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="C9">
-        <v>92.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="D9">
-        <v>97</v>
+        <v>96.5</v>
       </c>
       <c r="E9">
-        <v>41.2</v>
+        <v>43.3</v>
       </c>
       <c r="F9">
-        <v>26.6</v>
+        <v>24.1</v>
       </c>
       <c r="G9">
-        <v>22.7</v>
+        <v>17</v>
+      </c>
+      <c r="H9">
+        <v>17.5</v>
       </c>
     </row>
   </sheetData>
@@ -1935,28 +1971,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1964,28 +2000,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D2">
-        <v>108.55</v>
+        <v>107.67</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>129.52</v>
+        <v>126.08</v>
       </c>
       <c r="G2">
-        <v>0.511</v>
+        <v>0.542</v>
       </c>
       <c r="H2">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1993,28 +2029,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D3">
-        <v>111.65</v>
+        <v>104.82</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>129</v>
+        <v>125.46</v>
       </c>
       <c r="G3">
-        <v>0.511</v>
+        <v>0.5</v>
       </c>
       <c r="H3">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2022,28 +2058,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D4">
-        <v>121.76</v>
+        <v>129.28</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>127.98</v>
+        <v>124.54</v>
       </c>
       <c r="G4">
-        <v>0.467</v>
+        <v>0.479</v>
       </c>
       <c r="H4">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2051,28 +2087,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D5">
-        <v>139.86</v>
+        <v>117.15</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>125.4</v>
+        <v>123.08</v>
       </c>
       <c r="G5">
-        <v>0.533</v>
+        <v>0.479</v>
       </c>
       <c r="H5">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2080,28 +2116,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D6">
-        <v>127.53</v>
+        <v>119.55</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6">
-        <v>125.5</v>
+        <v>122.48</v>
       </c>
       <c r="G6">
-        <v>0.556</v>
+        <v>0.521</v>
       </c>
       <c r="H6">
-        <v>-1.6</v>
+        <v>-0.2</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2109,28 +2145,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D7">
-        <v>137.15</v>
+        <v>143.38</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7">
-        <v>124.54</v>
+        <v>121.02</v>
       </c>
       <c r="G7">
-        <v>0.467</v>
+        <v>0.521</v>
       </c>
       <c r="H7">
-        <v>-2.8</v>
+        <v>-0.6</v>
       </c>
       <c r="I7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2138,28 +2174,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D8">
-        <v>138.91</v>
+        <v>126.28</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F8">
-        <v>123.31</v>
+        <v>120.1</v>
       </c>
       <c r="G8">
-        <v>0.422</v>
+        <v>0.5</v>
       </c>
       <c r="H8">
-        <v>-3.4</v>
+        <v>-5.1</v>
       </c>
       <c r="I8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2167,28 +2203,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D9">
-        <v>124.15</v>
+        <v>134.08</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F9">
-        <v>124.31</v>
+        <v>119.48</v>
       </c>
       <c r="G9">
-        <v>0.533</v>
+        <v>0.458</v>
       </c>
       <c r="H9">
-        <v>-3.8</v>
+        <v>-5.9</v>
       </c>
       <c r="I9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2203,31 +2239,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2235,16 +2271,16 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C2">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D2">
-        <v>138.912</v>
+        <v>134.0766666666667</v>
       </c>
       <c r="E2">
-        <v>694.5599999999999</v>
+        <v>804.4599999999999</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -2253,10 +2289,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2264,16 +2300,16 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C3">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D3">
-        <v>137.148</v>
+        <v>129.2833333333333</v>
       </c>
       <c r="E3">
-        <v>685.74</v>
+        <v>775.7</v>
       </c>
       <c r="F3">
         <v>100</v>
@@ -2282,10 +2318,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2293,83 +2329,83 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C4">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D4">
-        <v>139.86</v>
+        <v>143.3766666666667</v>
       </c>
       <c r="E4">
-        <v>699.3</v>
+        <v>860.26</v>
       </c>
       <c r="F4">
-        <v>99.7</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C5">
-        <v>0.6</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D5">
-        <v>121.756</v>
+        <v>126.2833333333333</v>
       </c>
       <c r="E5">
-        <v>608.78</v>
+        <v>757.7</v>
       </c>
       <c r="F5">
-        <v>92.30000000000001</v>
+        <v>91.60000000000001</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="H5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C6">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>127.528</v>
+        <v>117.1533333333333</v>
       </c>
       <c r="E6">
-        <v>637.64</v>
+        <v>702.92</v>
       </c>
       <c r="F6">
-        <v>79.60000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="G6">
-        <v>8.6</v>
+        <v>2.6</v>
       </c>
       <c r="H6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I6" t="s">
         <v>73</v>
@@ -2380,28 +2416,28 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C7">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D7">
-        <v>124.152</v>
+        <v>119.55</v>
       </c>
       <c r="E7">
-        <v>620.76</v>
+        <v>717.3</v>
       </c>
       <c r="F7">
-        <v>69.5</v>
+        <v>78.10000000000001</v>
       </c>
       <c r="G7">
-        <v>12.2</v>
+        <v>5.899999999999999</v>
       </c>
       <c r="H7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2409,28 +2445,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C8">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D8">
-        <v>111.652</v>
+        <v>107.6733333333333</v>
       </c>
       <c r="E8">
-        <v>558.26</v>
+        <v>646.04</v>
       </c>
       <c r="F8">
-        <v>34.8</v>
+        <v>24.3</v>
       </c>
       <c r="G8">
-        <v>31.5</v>
+        <v>37.1</v>
       </c>
       <c r="H8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2438,28 +2474,28 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D9">
-        <v>108.552</v>
+        <v>104.8233333333333</v>
       </c>
       <c r="E9">
-        <v>542.7600000000001</v>
+        <v>628.9400000000001</v>
       </c>
       <c r="F9">
-        <v>24.1</v>
+        <v>18.6</v>
       </c>
       <c r="G9">
-        <v>45.7</v>
+        <v>51.6</v>
       </c>
       <c r="H9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2474,19 +2510,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2494,19 +2530,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2514,19 +2550,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2534,19 +2570,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2554,19 +2590,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2577,16 +2613,16 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D6">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2597,16 +2633,16 @@
         <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D7">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2617,16 +2653,16 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D8">
-        <v>-15</v>
+        <v>-24</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2637,16 +2673,16 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9">
-        <v>-26</v>
+        <v>-30</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -2656,78 +2692,87 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>91</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>12</v>
+      </c>
+      <c r="D2">
+        <v>16</v>
+      </c>
+      <c r="E2">
+        <v>9</v>
+      </c>
+      <c r="F2">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
         <v>3</v>
       </c>
-      <c r="B2">
-        <v>6</v>
-      </c>
-      <c r="C2">
-        <v>8</v>
-      </c>
-      <c r="D2">
+      <c r="C3">
+        <v>8</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
         <v>14</v>
       </c>
-      <c r="E2">
-        <v>18</v>
-      </c>
-      <c r="F2">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>12</v>
-      </c>
-      <c r="D3">
+      <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="G3">
         <v>16</v>
       </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="H3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -2736,42 +2781,48 @@
         <v>8</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
+        <v>6</v>
+      </c>
+      <c r="F4">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5">
         <v>14</v>
       </c>
-      <c r="F4">
-        <v>10</v>
-      </c>
-      <c r="G4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>8</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
       <c r="E5">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F5">
-        <v>9</v>
-      </c>
-      <c r="G5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>18</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
@@ -2790,11 +2841,14 @@
       <c r="F6">
         <v>-2</v>
       </c>
-      <c r="G6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="G6">
+        <v>-3</v>
+      </c>
+      <c r="H6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -2813,11 +2867,14 @@
       <c r="F7">
         <v>-8</v>
       </c>
-      <c r="G7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="G7">
+        <v>-4</v>
+      </c>
+      <c r="H7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -2836,11 +2893,14 @@
       <c r="F8">
         <v>-15</v>
       </c>
-      <c r="G8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="G8">
+        <v>-24</v>
+      </c>
+      <c r="H8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -2859,8 +2919,11 @@
       <c r="F9">
         <v>-26</v>
       </c>
-      <c r="G9" t="s">
-        <v>83</v>
+      <c r="G9">
+        <v>-30</v>
+      </c>
+      <c r="H9" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/EBC League 2026.xlsx
+++ b/data/leagues/EBC League 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="104">
   <si>
     <t>P90 Asiimov</t>
   </si>
@@ -49,25 +49,25 @@
     <t xml:space="preserve">First down syndrome </t>
   </si>
   <si>
-    <t>2-4-0</t>
-  </si>
-  <si>
-    <t>3-3-0</t>
-  </si>
-  <si>
-    <t>1-5-0</t>
-  </si>
-  <si>
-    <t>4-2-0</t>
-  </si>
-  <si>
-    <t>5-1-0</t>
-  </si>
-  <si>
-    <t>0-6-0</t>
-  </si>
-  <si>
-    <t>6-0-0</t>
+    <t>3-4-0</t>
+  </si>
+  <si>
+    <t>2-5-0</t>
+  </si>
+  <si>
+    <t>1-6-0</t>
+  </si>
+  <si>
+    <t>5-2-0</t>
+  </si>
+  <si>
+    <t>4-3-0</t>
+  </si>
+  <si>
+    <t>6-1-0</t>
+  </si>
+  <si>
+    <t>7-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -136,6 +136,9 @@
     <t>Week_7</t>
   </si>
   <si>
+    <t>Week_8</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -163,24 +166,24 @@
     <t>Alina Wise</t>
   </si>
   <si>
+    <t>Kate Zacierka</t>
+  </si>
+  <si>
+    <t>Mike Zacierka</t>
+  </si>
+  <si>
     <t>jack meehan</t>
   </si>
   <si>
-    <t>Kate Zacierka</t>
-  </si>
-  <si>
-    <t>Mike Zacierka</t>
-  </si>
-  <si>
     <t>Derek Alcavage</t>
   </si>
   <si>
+    <t>Gianpierre Lopez</t>
+  </si>
+  <si>
     <t>Louis Rodriguez</t>
   </si>
   <si>
-    <t>Gianpierre Lopez</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -205,45 +208,51 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>9.3-4.7-0.1</t>
-  </si>
-  <si>
-    <t>9.4-4.5-0.1</t>
-  </si>
-  <si>
-    <t>9.8-4.1-0.1</t>
-  </si>
-  <si>
-    <t>6.6-7.3-0.1</t>
-  </si>
-  <si>
-    <t>6.4-7.5-0.1</t>
-  </si>
-  <si>
-    <t>5.7-8.2-0.1</t>
-  </si>
-  <si>
-    <t>4.4-9.6-0.1</t>
-  </si>
-  <si>
-    <t>4.2-9.8-0.1</t>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>6-1</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>9.6-4.3-0.1</t>
+  </si>
+  <si>
+    <t>9.7-4.3-0.1</t>
+  </si>
+  <si>
+    <t>8.6-5.3-0.1</t>
+  </si>
+  <si>
+    <t>7.2-6.7-0.1</t>
+  </si>
+  <si>
+    <t>6.4-7.6-0.1</t>
+  </si>
+  <si>
+    <t>5.9-8.1-0.1</t>
+  </si>
+  <si>
+    <t>4.3-9.6-0.1</t>
+  </si>
+  <si>
+    <t>4.1-9.8-0.1</t>
   </si>
   <si>
     <t>10-4</t>
   </si>
   <si>
+    <t>9-5</t>
+  </si>
+  <si>
     <t>7-7</t>
   </si>
   <si>
@@ -262,25 +271,28 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑4</t>
+    <t>↑10</t>
+  </si>
+  <si>
+    <t>↑5</t>
+  </si>
+  <si>
+    <t>↓10</t>
+  </si>
+  <si>
+    <t>↓8</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>↓4</t>
   </si>
   <si>
     <t>↑6</t>
   </si>
   <si>
-    <t>↑7</t>
-  </si>
-  <si>
-    <t>↓6</t>
-  </si>
-  <si>
-    <t>↓1</t>
-  </si>
-  <si>
-    <t>↓9</t>
-  </si>
-  <si>
-    <t>↓4</t>
+    <t>↑2</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -299,6 +311,9 @@
   </si>
   <si>
     <t>Week 6</t>
+  </si>
+  <si>
+    <t>Week 7</t>
   </si>
   <si>
     <t>Week</t>
@@ -720,10 +735,10 @@
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
@@ -740,7 +755,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
@@ -749,19 +764,19 @@
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
         <v>8</v>
       </c>
       <c r="G3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" t="s">
         <v>12</v>
-      </c>
-      <c r="I3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -778,19 +793,19 @@
         <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
         <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -798,28 +813,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
         <v>12</v>
       </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
         <v>11</v>
       </c>
       <c r="G5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" t="s">
         <v>12</v>
       </c>
-      <c r="H5" t="s">
-        <v>11</v>
-      </c>
       <c r="I5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -827,28 +842,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
         <v>12</v>
       </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -862,22 +877,22 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
         <v>9</v>
       </c>
-      <c r="G7" t="s">
-        <v>8</v>
-      </c>
       <c r="H7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -888,7 +903,7 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -897,13 +912,13 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" t="s">
         <v>9</v>
-      </c>
-      <c r="H8" t="s">
-        <v>8</v>
       </c>
       <c r="I8" t="s">
         <v>10</v>
@@ -917,25 +932,25 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
         <v>9</v>
       </c>
-      <c r="D9" t="s">
-        <v>8</v>
-      </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -945,30 +960,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1125,6 +1140,32 @@
       </c>
       <c r="H7" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>6</v>
+      </c>
+      <c r="F8">
+        <v>4</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1156,7 +1197,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1.875</v>
+        <v>2.125</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -1167,10 +1208,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>2.625</v>
+        <v>3.25</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -1181,13 +1222,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>2.75</v>
+        <v>3.375</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1195,13 +1236,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>2.875</v>
+        <v>3.5</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1212,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>3.625</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
@@ -1223,13 +1264,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>3.25</v>
+        <v>3.875</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1237,13 +1278,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>3.75</v>
+        <v>4.125</v>
       </c>
       <c r="D8" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1254,10 +1295,10 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>3.875</v>
+        <v>4.125</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1289,16 +1330,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="D2">
-        <v>-0.75</v>
+        <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1306,16 +1347,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>4.125</v>
+        <v>4.5</v>
       </c>
       <c r="D3">
-        <v>0.125</v>
+        <v>-1.5</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1323,16 +1364,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1340,16 +1381,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1360,10 +1401,10 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>2.75</v>
+        <v>3.375</v>
       </c>
       <c r="D6">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1377,13 +1418,13 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="D7">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1394,13 +1435,13 @@
         <v>5</v>
       </c>
       <c r="C8">
-        <v>1.75</v>
+        <v>2.375</v>
       </c>
       <c r="D8">
-        <v>-0.25</v>
+        <v>0.375</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1411,13 +1452,13 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>1.375</v>
+        <v>1.75</v>
       </c>
       <c r="D9">
-        <v>-0.625</v>
+        <v>-0.25</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1467,22 +1508,22 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>22.9</v>
+        <v>47.4</v>
       </c>
       <c r="C2">
-        <v>37.2</v>
+        <v>27</v>
       </c>
       <c r="D2">
-        <v>29.3</v>
+        <v>17.6</v>
       </c>
       <c r="E2">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="G2">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1499,22 +1540,22 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>24</v>
+        <v>30.6</v>
       </c>
       <c r="C3">
-        <v>30.1</v>
+        <v>34.1</v>
       </c>
       <c r="D3">
-        <v>33.9</v>
+        <v>21.8</v>
       </c>
       <c r="E3">
-        <v>8.699999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F3">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1531,31 +1572,31 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>52.8</v>
+        <v>19.4</v>
       </c>
       <c r="C4">
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="D4">
-        <v>15.2</v>
+        <v>32.1</v>
       </c>
       <c r="E4">
-        <v>2.7</v>
+        <v>15.7</v>
       </c>
       <c r="F4">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>0.3</v>
       </c>
-      <c r="H4">
-        <v>0.1</v>
-      </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>99.90000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1563,100 +1604,100 @@
         <v>0</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="C5">
-        <v>3.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D5">
-        <v>10.9</v>
+        <v>19.1</v>
       </c>
       <c r="E5">
-        <v>36.3</v>
+        <v>38.6</v>
       </c>
       <c r="F5">
-        <v>27.4</v>
+        <v>20.3</v>
       </c>
       <c r="G5">
-        <v>13.3</v>
+        <v>8.1</v>
       </c>
       <c r="H5">
-        <v>5.6</v>
+        <v>2.2</v>
       </c>
       <c r="I5">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J5">
-        <v>91.59999999999999</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B6">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="C6">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="D6">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="E6">
-        <v>23.7</v>
+        <v>16.4</v>
       </c>
       <c r="F6">
-        <v>30.6</v>
+        <v>36.7</v>
       </c>
       <c r="G6">
-        <v>25</v>
+        <v>26.3</v>
       </c>
       <c r="H6">
-        <v>9.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J6">
-        <v>87.5</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C7">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="D7">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="E7">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="F7">
-        <v>24.5</v>
+        <v>26.7</v>
       </c>
       <c r="G7">
-        <v>33.3</v>
+        <v>39.5</v>
       </c>
       <c r="H7">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="I7">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="J7">
-        <v>78.09999999999999</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1665,30 +1706,30 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="F8">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="G8">
-        <v>14.8</v>
+        <v>13</v>
       </c>
       <c r="H8">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="I8">
-        <v>37.1</v>
+        <v>42.4</v>
       </c>
       <c r="J8">
-        <v>24.3</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1697,25 +1738,25 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="F9">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="G9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H9">
-        <v>29.8</v>
+        <v>35.5</v>
       </c>
       <c r="I9">
-        <v>51.6</v>
+        <v>50</v>
       </c>
       <c r="J9">
-        <v>18.6</v>
+        <v>14.5</v>
       </c>
     </row>
   </sheetData>
@@ -1725,10 +1766,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
         <v>30</v>
       </c>
@@ -1750,8 +1791,11 @@
       <c r="H1" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1765,19 +1809,22 @@
         <v>100</v>
       </c>
       <c r="E2">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="F2">
         <v>100</v>
       </c>
       <c r="G2">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1802,8 +1849,11 @@
       <c r="H3">
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3">
+        <v>99.90000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1814,27 +1864,30 @@
         <v>100</v>
       </c>
       <c r="D4">
-        <v>95.5</v>
+        <v>95.39999999999999</v>
       </c>
       <c r="E4">
-        <v>99.7</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F4">
-        <v>99.59999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="H4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>99.3</v>
+      </c>
+      <c r="I4">
+        <v>99.40000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B5">
-        <v>93.89999999999999</v>
+        <v>92.80000000000001</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -1843,120 +1896,135 @@
         <v>97.8</v>
       </c>
       <c r="E5">
-        <v>94.5</v>
+        <v>93</v>
       </c>
       <c r="F5">
-        <v>81.69999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="G5">
-        <v>91.7</v>
+        <v>91.5</v>
       </c>
       <c r="H5">
-        <v>93.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>97.8</v>
+      </c>
+      <c r="I5">
+        <v>96.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>51</v>
+      </c>
+      <c r="C6">
+        <v>9.4</v>
+      </c>
+      <c r="D6">
+        <v>13.2</v>
+      </c>
+      <c r="E6">
+        <v>9.9</v>
+      </c>
+      <c r="F6">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="G6">
+        <v>80.2</v>
+      </c>
+      <c r="H6">
+        <v>88.7</v>
+      </c>
+      <c r="I6">
+        <v>88.09999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6">
-        <v>59.9</v>
-      </c>
-      <c r="C6">
-        <v>84.89999999999999</v>
-      </c>
-      <c r="D6">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="E6">
-        <v>78.5</v>
-      </c>
-      <c r="F6">
-        <v>93</v>
-      </c>
-      <c r="G6">
-        <v>85.8</v>
-      </c>
-      <c r="H6">
-        <v>90.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="B7">
-        <v>49.6</v>
+        <v>60.6</v>
       </c>
       <c r="C7">
-        <v>10.4</v>
+        <v>87</v>
       </c>
       <c r="D7">
-        <v>14.8</v>
+        <v>76.2</v>
       </c>
       <c r="E7">
-        <v>10.5</v>
+        <v>81.10000000000001</v>
       </c>
       <c r="F7">
-        <v>70.8</v>
+        <v>91.60000000000001</v>
       </c>
       <c r="G7">
-        <v>82.89999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="H7">
-        <v>77.3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>80.10000000000001</v>
+      </c>
+      <c r="I7">
+        <v>81.89999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>93.89999999999999</v>
+      </c>
+      <c r="C8">
+        <v>91.3</v>
+      </c>
+      <c r="D8">
+        <v>96.89999999999999</v>
+      </c>
+      <c r="E8">
+        <v>43.6</v>
+      </c>
+      <c r="F8">
+        <v>25.4</v>
+      </c>
+      <c r="G8">
+        <v>16.9</v>
+      </c>
+      <c r="H8">
+        <v>18.3</v>
+      </c>
+      <c r="I8">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8">
-        <v>1.4</v>
-      </c>
-      <c r="C8">
-        <v>12.2</v>
-      </c>
-      <c r="D8">
-        <v>22</v>
-      </c>
-      <c r="E8">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="F8">
-        <v>30.9</v>
-      </c>
-      <c r="G8">
-        <v>22.8</v>
-      </c>
-      <c r="H8">
-        <v>21.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="B9">
-        <v>95.19999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="C9">
-        <v>92.5</v>
+        <v>12.3</v>
       </c>
       <c r="D9">
-        <v>96.5</v>
+        <v>20.5</v>
       </c>
       <c r="E9">
-        <v>43.3</v>
+        <v>73</v>
       </c>
       <c r="F9">
-        <v>24.1</v>
+        <v>28.8</v>
       </c>
       <c r="G9">
-        <v>17</v>
+        <v>25.2</v>
       </c>
       <c r="H9">
-        <v>17.5</v>
+        <v>15.8</v>
+      </c>
+      <c r="I9">
+        <v>14.6</v>
       </c>
     </row>
   </sheetData>
@@ -1974,25 +2042,25 @@
         <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2003,25 +2071,25 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2">
-        <v>107.67</v>
+        <v>107.85</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>126.08</v>
+        <v>123.19</v>
       </c>
       <c r="G2">
-        <v>0.542</v>
+        <v>0.531</v>
       </c>
       <c r="H2">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2032,25 +2100,25 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D3">
-        <v>104.82</v>
+        <v>108.32</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>125.46</v>
+        <v>123.13</v>
       </c>
       <c r="G3">
-        <v>0.5</v>
+        <v>0.531</v>
       </c>
       <c r="H3">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2058,28 +2126,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4">
-        <v>129.28</v>
+        <v>115.91</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>124.54</v>
+        <v>122.04</v>
       </c>
       <c r="G4">
-        <v>0.479</v>
+        <v>0.51</v>
       </c>
       <c r="H4">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2087,28 +2155,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5">
+        <v>118.97</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>121.6</v>
+      </c>
+      <c r="G5">
+        <v>0.51</v>
+      </c>
+      <c r="H5">
+        <v>0.4</v>
+      </c>
+      <c r="I5">
         <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5">
-        <v>117.15</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>123.08</v>
-      </c>
-      <c r="G5">
-        <v>0.479</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2116,28 +2184,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D6">
-        <v>119.55</v>
+        <v>122.71</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>122.48</v>
+        <v>121.07</v>
       </c>
       <c r="G6">
-        <v>0.521</v>
+        <v>0.449</v>
       </c>
       <c r="H6">
-        <v>-0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2148,25 +2216,25 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7">
-        <v>143.38</v>
+        <v>134.4</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>121.02</v>
+        <v>119.4</v>
       </c>
       <c r="G7">
-        <v>0.521</v>
+        <v>0.49</v>
       </c>
       <c r="H7">
-        <v>-0.6</v>
+        <v>-0.9</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2174,28 +2242,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8">
-        <v>126.28</v>
+        <v>133.86</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F8">
-        <v>120.1</v>
+        <v>119.48</v>
       </c>
       <c r="G8">
-        <v>0.5</v>
+        <v>0.469</v>
       </c>
       <c r="H8">
-        <v>-5.1</v>
+        <v>-3</v>
       </c>
       <c r="I8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2203,28 +2271,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9">
-        <v>134.08</v>
+        <v>128.17</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F9">
-        <v>119.48</v>
+        <v>120.29</v>
       </c>
       <c r="G9">
-        <v>0.458</v>
+        <v>0.51</v>
       </c>
       <c r="H9">
-        <v>-5.9</v>
+        <v>-3.7</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2242,28 +2310,28 @@
         <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2271,16 +2339,16 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C2">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D2">
-        <v>134.0766666666667</v>
+        <v>133.8628571428571</v>
       </c>
       <c r="E2">
-        <v>804.4599999999999</v>
+        <v>937.04</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -2289,10 +2357,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2300,16 +2368,16 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C3">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D3">
-        <v>129.2833333333333</v>
+        <v>122.7142857142857</v>
       </c>
       <c r="E3">
-        <v>775.7</v>
+        <v>859</v>
       </c>
       <c r="F3">
         <v>100</v>
@@ -2318,10 +2386,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2329,28 +2397,28 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C4">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D4">
-        <v>143.3766666666667</v>
+        <v>134.3971428571429</v>
       </c>
       <c r="E4">
-        <v>860.26</v>
+        <v>940.78</v>
       </c>
       <c r="F4">
-        <v>99.90000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2358,144 +2426,144 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C5">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D5">
-        <v>126.2833333333333</v>
+        <v>128.1742857142857</v>
       </c>
       <c r="E5">
-        <v>757.7</v>
+        <v>897.22</v>
       </c>
       <c r="F5">
-        <v>91.60000000000001</v>
+        <v>97</v>
       </c>
       <c r="G5">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D6">
-        <v>117.1533333333333</v>
+        <v>118.9714285714286</v>
       </c>
       <c r="E6">
-        <v>702.92</v>
+        <v>832.8</v>
       </c>
       <c r="F6">
-        <v>87.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G6">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="H6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I6" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C7">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D7">
-        <v>119.55</v>
+        <v>115.9114285714286</v>
       </c>
       <c r="E7">
-        <v>717.3</v>
+        <v>811.38</v>
       </c>
       <c r="F7">
-        <v>78.10000000000001</v>
+        <v>81</v>
       </c>
       <c r="G7">
-        <v>5.899999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="H7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C8">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D8">
-        <v>107.6733333333333</v>
+        <v>108.3228571428571</v>
       </c>
       <c r="E8">
-        <v>646.04</v>
+        <v>758.26</v>
       </c>
       <c r="F8">
-        <v>24.3</v>
+        <v>18.9</v>
       </c>
       <c r="G8">
-        <v>37.1</v>
+        <v>42.4</v>
       </c>
       <c r="H8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C9">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D9">
-        <v>104.8233333333333</v>
+        <v>107.8485714285714</v>
       </c>
       <c r="E9">
-        <v>628.9400000000001</v>
+        <v>754.9399999999999</v>
       </c>
       <c r="F9">
-        <v>18.6</v>
+        <v>14.5</v>
       </c>
       <c r="G9">
-        <v>51.6</v>
+        <v>50</v>
       </c>
       <c r="H9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2513,16 +2581,16 @@
         <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2530,19 +2598,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2550,19 +2618,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2570,19 +2638,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
         <v>50</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2593,16 +2661,16 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2622,7 +2690,7 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2636,13 +2704,13 @@
         <v>47</v>
       </c>
       <c r="D7">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2653,16 +2721,16 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8">
-        <v>-24</v>
+        <v>-18</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2673,16 +2741,16 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9">
-        <v>-30</v>
+        <v>-28</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -2692,87 +2760,96 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>96</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E2">
+        <v>6</v>
+      </c>
+      <c r="F2">
         <v>9</v>
-      </c>
-      <c r="F2">
-        <v>12</v>
       </c>
       <c r="G2">
         <v>16</v>
       </c>
-      <c r="H2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="H2">
+        <v>26</v>
+      </c>
+      <c r="I2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
         <v>4</v>
       </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
       <c r="C3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>16</v>
       </c>
-      <c r="H3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="H3">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -2781,22 +2858,25 @@
         <v>8</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>16</v>
       </c>
-      <c r="H4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="H4">
+        <v>6</v>
+      </c>
+      <c r="I4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -2818,11 +2898,14 @@
       <c r="G5">
         <v>12</v>
       </c>
-      <c r="H5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
@@ -2844,11 +2927,14 @@
       <c r="G6">
         <v>-3</v>
       </c>
-      <c r="H6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="H6">
+        <v>-3</v>
+      </c>
+      <c r="I6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -2870,11 +2956,14 @@
       <c r="G7">
         <v>-4</v>
       </c>
-      <c r="H7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="H7">
+        <v>-8</v>
+      </c>
+      <c r="I7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -2896,11 +2985,14 @@
       <c r="G8">
         <v>-24</v>
       </c>
-      <c r="H8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="H8">
+        <v>-18</v>
+      </c>
+      <c r="I8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -2922,8 +3014,11 @@
       <c r="G9">
         <v>-30</v>
       </c>
-      <c r="H9" t="s">
-        <v>85</v>
+      <c r="H9">
+        <v>-28</v>
+      </c>
+      <c r="I9" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/EBC League 2026.xlsx
+++ b/data/leagues/EBC League 2026.xlsx
@@ -223,28 +223,28 @@
     <t>2-5</t>
   </si>
   <si>
+    <t>9.7-4.3-0.1</t>
+  </si>
+  <si>
     <t>9.6-4.3-0.1</t>
   </si>
   <si>
-    <t>9.7-4.3-0.1</t>
-  </si>
-  <si>
-    <t>8.6-5.3-0.1</t>
+    <t>8.5-5.4-0.1</t>
   </si>
   <si>
     <t>7.2-6.7-0.1</t>
   </si>
   <si>
-    <t>6.4-7.6-0.1</t>
-  </si>
-  <si>
-    <t>5.9-8.1-0.1</t>
+    <t>6.3-7.7-0.1</t>
+  </si>
+  <si>
+    <t>6.0-7.9-0.1</t>
   </si>
   <si>
     <t>4.3-9.6-0.1</t>
   </si>
   <si>
-    <t>4.1-9.8-0.1</t>
+    <t>4.2-9.7-0.1</t>
   </si>
   <si>
     <t>10-4</t>
@@ -1508,22 +1508,22 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>47.4</v>
+        <v>49.7</v>
       </c>
       <c r="C2">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="D2">
-        <v>17.6</v>
+        <v>16.2</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="F2">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1540,31 +1540,31 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>30.6</v>
+        <v>28.7</v>
       </c>
       <c r="C3">
-        <v>34.1</v>
+        <v>35</v>
       </c>
       <c r="D3">
-        <v>21.8</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>9.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G3">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1572,31 +1572,31 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="C4">
-        <v>27</v>
+        <v>26.3</v>
       </c>
       <c r="D4">
-        <v>32.1</v>
+        <v>31.4</v>
       </c>
       <c r="E4">
-        <v>15.7</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="H4">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>99.7</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1607,28 +1607,28 @@
         <v>2.1</v>
       </c>
       <c r="C5">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D5">
-        <v>19.1</v>
+        <v>18.6</v>
       </c>
       <c r="E5">
-        <v>38.6</v>
+        <v>39.4</v>
       </c>
       <c r="F5">
-        <v>20.3</v>
+        <v>19.3</v>
       </c>
       <c r="G5">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="H5">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="I5">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J5">
-        <v>97</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1636,31 +1636,31 @@
         <v>1</v>
       </c>
       <c r="B6">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="C6">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="D6">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="E6">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="F6">
-        <v>36.7</v>
+        <v>33.2</v>
       </c>
       <c r="G6">
-        <v>26.3</v>
+        <v>28.8</v>
       </c>
       <c r="H6">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I6">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J6">
-        <v>88.90000000000001</v>
+        <v>87.59999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1668,31 +1668,31 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C7">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="D7">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="E7">
-        <v>11.5</v>
+        <v>10.3</v>
       </c>
       <c r="F7">
-        <v>26.7</v>
+        <v>30.5</v>
       </c>
       <c r="G7">
-        <v>39.5</v>
+        <v>37.1</v>
       </c>
       <c r="H7">
-        <v>14.5</v>
+        <v>13.7</v>
       </c>
       <c r="I7">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J7">
-        <v>81</v>
+        <v>82.09999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1703,28 +1703,28 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D8">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E8">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="F8">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="H8">
-        <v>38.7</v>
+        <v>39.1</v>
       </c>
       <c r="I8">
-        <v>42.4</v>
+        <v>42.7</v>
       </c>
       <c r="J8">
-        <v>18.9</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1735,28 +1735,28 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E9">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="F9">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="G9">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="H9">
-        <v>35.5</v>
+        <v>34.7</v>
       </c>
       <c r="I9">
-        <v>50</v>
+        <v>49.2</v>
       </c>
       <c r="J9">
-        <v>14.5</v>
+        <v>16.1</v>
       </c>
     </row>
   </sheetData>
@@ -1847,7 +1847,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I3">
         <v>99.90000000000001</v>
@@ -1876,10 +1876,10 @@
         <v>99.8</v>
       </c>
       <c r="H4">
+        <v>99.7</v>
+      </c>
+      <c r="I4">
         <v>99.3</v>
-      </c>
-      <c r="I4">
-        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1905,10 +1905,10 @@
         <v>91.5</v>
       </c>
       <c r="H5">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="I5">
-        <v>96.3</v>
+        <v>97.39999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1934,10 +1934,10 @@
         <v>80.2</v>
       </c>
       <c r="H6">
-        <v>88.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I6">
-        <v>88.09999999999999</v>
+        <v>86.59999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1963,10 +1963,10 @@
         <v>86.5</v>
       </c>
       <c r="H7">
-        <v>80.10000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="I7">
-        <v>81.89999999999999</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1992,10 +1992,10 @@
         <v>16.9</v>
       </c>
       <c r="H8">
-        <v>18.3</v>
+        <v>19.1</v>
       </c>
       <c r="I8">
-        <v>19.8</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2021,10 +2021,10 @@
         <v>25.2</v>
       </c>
       <c r="H9">
-        <v>15.8</v>
+        <v>13.5</v>
       </c>
       <c r="I9">
-        <v>14.6</v>
+        <v>17.7</v>
       </c>
     </row>
   </sheetData>
@@ -2380,7 +2380,7 @@
         <v>859</v>
       </c>
       <c r="F3">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>940.78</v>
       </c>
       <c r="F4">
-        <v>99.7</v>
+        <v>99.8</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>897.22</v>
       </c>
       <c r="F5">
-        <v>97</v>
+        <v>96.3</v>
       </c>
       <c r="G5">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="H5" t="s">
         <v>69</v>
@@ -2467,10 +2467,10 @@
         <v>832.8</v>
       </c>
       <c r="F6">
-        <v>88.90000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="G6">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="H6" t="s">
         <v>70</v>
@@ -2496,10 +2496,10 @@
         <v>811.38</v>
       </c>
       <c r="F7">
-        <v>81</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G7">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="H7" t="s">
         <v>71</v>
@@ -2525,10 +2525,10 @@
         <v>758.26</v>
       </c>
       <c r="F8">
-        <v>18.9</v>
+        <v>18.2</v>
       </c>
       <c r="G8">
-        <v>42.4</v>
+        <v>42.7</v>
       </c>
       <c r="H8" t="s">
         <v>72</v>
@@ -2554,10 +2554,10 @@
         <v>754.9399999999999</v>
       </c>
       <c r="F9">
-        <v>14.5</v>
+        <v>16.1</v>
       </c>
       <c r="G9">
-        <v>50</v>
+        <v>49.2</v>
       </c>
       <c r="H9" t="s">
         <v>73</v>
